--- a/output/walk_forward_reports/parameter_stability.xlsx
+++ b/output/walk_forward_reports/parameter_stability.xlsx
@@ -1,15 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\qqq\output\walk_forward_reports\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C30A90F0-29E4-4A3F-8ED3-AEDB82FCBA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$1</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -55,6 +64,9 @@
     <t>equal</t>
   </si>
   <si>
+    <t>mvo</t>
+  </si>
+  <si>
     <t>factor_score</t>
   </si>
   <si>
@@ -64,379 +76,383 @@
     <t>min_variance</t>
   </si>
   <si>
-    <t>mvo</t>
+    <t>equal_5G_Top3_P20d</t>
+  </si>
+  <si>
+    <t>equal_5G_Top2_P30d</t>
+  </si>
+  <si>
+    <t>mvo_10G_Top3_P10d</t>
+  </si>
+  <si>
+    <t>factor_score_5G_Top3_P20d</t>
+  </si>
+  <si>
+    <t>factor_score_5G_Top2_P30d</t>
+  </si>
+  <si>
+    <t>equal_5G_Top3_P60d</t>
+  </si>
+  <si>
+    <t>max_return_5G_Top3_P60d</t>
+  </si>
+  <si>
+    <t>mvo_5G_Top3_P60d</t>
+  </si>
+  <si>
+    <t>min_variance_5G_Top3_P60d</t>
+  </si>
+  <si>
+    <t>mvo_10G_Top3_P30d</t>
+  </si>
+  <si>
+    <t>factor_score_5G_Top3_P60d</t>
+  </si>
+  <si>
+    <t>equal_10G_Top3_P60d</t>
+  </si>
+  <si>
+    <t>min_variance_10G_Top3_P60d</t>
+  </si>
+  <si>
+    <t>max_return_10G_Top3_P60d</t>
+  </si>
+  <si>
+    <t>mvo_10G_Top3_P60d</t>
+  </si>
+  <si>
+    <t>max_return_10G_Top3_P30d</t>
+  </si>
+  <si>
+    <t>factor_score_10G_Top3_P30d</t>
+  </si>
+  <si>
+    <t>max_return_5G_Top2_P30d</t>
+  </si>
+  <si>
+    <t>min_variance_5G_Top3_P20d</t>
+  </si>
+  <si>
+    <t>mvo_5G_Top2_P30d</t>
+  </si>
+  <si>
+    <t>equal_10G_Top3_P30d</t>
+  </si>
+  <si>
+    <t>min_variance_10G_Top1_P60d</t>
+  </si>
+  <si>
+    <t>max_return_10G_Top1_P60d</t>
+  </si>
+  <si>
+    <t>mvo_10G_Top1_P60d</t>
+  </si>
+  <si>
+    <t>equal_10G_Top1_P60d</t>
+  </si>
+  <si>
+    <t>equal_10G_Top2_P20d</t>
+  </si>
+  <si>
+    <t>mvo_5G_Top3_P20d</t>
+  </si>
+  <si>
+    <t>max_return_10G_Top3_P10d</t>
+  </si>
+  <si>
+    <t>factor_score_5G_Top1_P10d</t>
+  </si>
+  <si>
+    <t>factor_score_10G_Top1_P10d</t>
+  </si>
+  <si>
+    <t>factor_score_10G_Top2_P20d</t>
+  </si>
+  <si>
+    <t>mvo_5G_Top1_P10d</t>
+  </si>
+  <si>
+    <t>equal_10G_Top1_P10d</t>
+  </si>
+  <si>
+    <t>mvo_10G_Top1_P10d</t>
+  </si>
+  <si>
+    <t>factor_score_10G_Top3_P10d</t>
+  </si>
+  <si>
+    <t>max_return_5G_Top2_P60d</t>
+  </si>
+  <si>
+    <t>equal_5G_Top2_P60d</t>
+  </si>
+  <si>
+    <t>min_variance_5G_Top2_P60d</t>
+  </si>
+  <si>
+    <t>mvo_5G_Top2_P60d</t>
+  </si>
+  <si>
+    <t>factor_score_5G_Top1_P60d</t>
   </si>
   <si>
     <t>equal_5G_Top1_P10d</t>
   </si>
   <si>
-    <t>factor_score_5G_Top1_P10d</t>
+    <t>factor_score_10G_Top3_P60d</t>
+  </si>
+  <si>
+    <t>factor_score_10G_Top1_P60d</t>
+  </si>
+  <si>
+    <t>factor_score_5G_Top3_P10d</t>
+  </si>
+  <si>
+    <t>min_variance_10G_Top2_P20d</t>
+  </si>
+  <si>
+    <t>factor_score_5G_Top2_P10d</t>
+  </si>
+  <si>
+    <t>factor_score_5G_Top2_P60d</t>
+  </si>
+  <si>
+    <t>mvo_5G_Top1_P60d</t>
+  </si>
+  <si>
+    <t>min_variance_5G_Top1_P60d</t>
+  </si>
+  <si>
+    <t>equal_5G_Top1_P60d</t>
+  </si>
+  <si>
+    <t>max_return_5G_Top1_P60d</t>
+  </si>
+  <si>
+    <t>min_variance_10G_Top3_P10d</t>
+  </si>
+  <si>
+    <t>mvo_5G_Top2_P10d</t>
+  </si>
+  <si>
+    <t>equal_5G_Top3_P10d</t>
+  </si>
+  <si>
+    <t>factor_score_5G_Top2_P20d</t>
+  </si>
+  <si>
+    <t>equal_5G_Top2_P10d</t>
+  </si>
+  <si>
+    <t>max_return_5G_Top2_P10d</t>
+  </si>
+  <si>
+    <t>factor_score_10G_Top1_P20d</t>
+  </si>
+  <si>
+    <t>equal_10G_Top3_P10d</t>
+  </si>
+  <si>
+    <t>min_variance_5G_Top2_P20d</t>
+  </si>
+  <si>
+    <t>mvo_10G_Top2_P10d</t>
+  </si>
+  <si>
+    <t>factor_score_5G_Top1_P20d</t>
+  </si>
+  <si>
+    <t>factor_score_5G_Top1_P30d</t>
+  </si>
+  <si>
+    <t>min_variance_5G_Top1_P10d</t>
+  </si>
+  <si>
+    <t>equal_10G_Top1_P30d</t>
+  </si>
+  <si>
+    <t>mvo_5G_Top1_P20d</t>
+  </si>
+  <si>
+    <t>equal_5G_Top1_P20d</t>
+  </si>
+  <si>
+    <t>factor_score_10G_Top1_P30d</t>
+  </si>
+  <si>
+    <t>equal_5G_Top1_P30d</t>
+  </si>
+  <si>
+    <t>equal_10G_Top2_P10d</t>
+  </si>
+  <si>
+    <t>mvo_5G_Top1_P30d</t>
+  </si>
+  <si>
+    <t>max_return_5G_Top1_P20d</t>
+  </si>
+  <si>
+    <t>mvo_10G_Top1_P30d</t>
+  </si>
+  <si>
+    <t>equal_5G_Top2_P20d</t>
+  </si>
+  <si>
+    <t>equal_5G_Top3_P30d</t>
+  </si>
+  <si>
+    <t>mvo_10G_Top1_P20d</t>
+  </si>
+  <si>
+    <t>max_return_10G_Top2_P20d</t>
+  </si>
+  <si>
+    <t>max_return_10G_Top1_P20d</t>
+  </si>
+  <si>
+    <t>equal_10G_Top1_P20d</t>
+  </si>
+  <si>
+    <t>min_variance_5G_Top2_P10d</t>
+  </si>
+  <si>
+    <t>mvo_5G_Top3_P30d</t>
+  </si>
+  <si>
+    <t>max_return_10G_Top2_P10d</t>
+  </si>
+  <si>
+    <t>mvo_10G_Top2_P20d</t>
+  </si>
+  <si>
+    <t>min_variance_10G_Top3_P30d</t>
+  </si>
+  <si>
+    <t>factor_score_5G_Top3_P30d</t>
+  </si>
+  <si>
+    <t>max_return_10G_Top1_P10d</t>
+  </si>
+  <si>
+    <t>max_return_5G_Top3_P20d</t>
+  </si>
+  <si>
+    <t>min_variance_5G_Top1_P30d</t>
+  </si>
+  <si>
+    <t>min_variance_10G_Top1_P10d</t>
+  </si>
+  <si>
+    <t>min_variance_5G_Top1_P20d</t>
+  </si>
+  <si>
+    <t>equal_10G_Top3_P20d</t>
+  </si>
+  <si>
+    <t>max_return_10G_Top2_P30d</t>
+  </si>
+  <si>
+    <t>factor_score_10G_Top2_P10d</t>
+  </si>
+  <si>
+    <t>max_return_10G_Top1_P30d</t>
+  </si>
+  <si>
+    <t>equal_10G_Top2_P30d</t>
+  </si>
+  <si>
+    <t>mvo_10G_Top2_P30d</t>
+  </si>
+  <si>
+    <t>min_variance_5G_Top3_P30d</t>
+  </si>
+  <si>
+    <t>min_variance_10G_Top1_P30d</t>
+  </si>
+  <si>
+    <t>factor_score_10G_Top3_P20d</t>
+  </si>
+  <si>
+    <t>factor_score_10G_Top2_P60d</t>
+  </si>
+  <si>
+    <t>mvo_10G_Top3_P20d</t>
+  </si>
+  <si>
+    <t>mvo_5G_Top2_P20d</t>
+  </si>
+  <si>
+    <t>max_return_5G_Top1_P30d</t>
+  </si>
+  <si>
+    <t>min_variance_10G_Top1_P20d</t>
+  </si>
+  <si>
+    <t>min_variance_5G_Top2_P30d</t>
   </si>
   <si>
     <t>max_return_5G_Top1_P10d</t>
   </si>
   <si>
-    <t>min_variance_5G_Top1_P10d</t>
-  </si>
-  <si>
-    <t>mvo_5G_Top1_P10d</t>
-  </si>
-  <si>
-    <t>equal_5G_Top1_P20d</t>
-  </si>
-  <si>
-    <t>factor_score_5G_Top1_P20d</t>
-  </si>
-  <si>
-    <t>max_return_5G_Top1_P20d</t>
-  </si>
-  <si>
-    <t>min_variance_5G_Top1_P20d</t>
-  </si>
-  <si>
-    <t>mvo_5G_Top1_P20d</t>
-  </si>
-  <si>
-    <t>equal_5G_Top1_P30d</t>
-  </si>
-  <si>
-    <t>factor_score_5G_Top1_P30d</t>
-  </si>
-  <si>
-    <t>max_return_5G_Top1_P30d</t>
-  </si>
-  <si>
-    <t>min_variance_5G_Top1_P30d</t>
-  </si>
-  <si>
-    <t>mvo_5G_Top1_P30d</t>
-  </si>
-  <si>
-    <t>equal_5G_Top1_P60d</t>
-  </si>
-  <si>
-    <t>factor_score_5G_Top1_P60d</t>
-  </si>
-  <si>
-    <t>max_return_5G_Top1_P60d</t>
-  </si>
-  <si>
-    <t>min_variance_5G_Top1_P60d</t>
-  </si>
-  <si>
-    <t>mvo_5G_Top1_P60d</t>
-  </si>
-  <si>
-    <t>equal_5G_Top2_P10d</t>
-  </si>
-  <si>
-    <t>factor_score_5G_Top2_P10d</t>
-  </si>
-  <si>
-    <t>max_return_5G_Top2_P10d</t>
-  </si>
-  <si>
-    <t>min_variance_5G_Top2_P10d</t>
-  </si>
-  <si>
-    <t>mvo_5G_Top2_P10d</t>
-  </si>
-  <si>
-    <t>equal_5G_Top2_P20d</t>
-  </si>
-  <si>
-    <t>factor_score_5G_Top2_P20d</t>
+    <t>min_variance_10G_Top2_P10d</t>
+  </si>
+  <si>
+    <t>min_variance_10G_Top3_P20d</t>
+  </si>
+  <si>
+    <t>max_return_5G_Top3_P10d</t>
+  </si>
+  <si>
+    <t>min_variance_5G_Top3_P10d</t>
+  </si>
+  <si>
+    <t>mvo_10G_Top2_P60d</t>
+  </si>
+  <si>
+    <t>equal_10G_Top2_P60d</t>
+  </si>
+  <si>
+    <t>min_variance_10G_Top2_P60d</t>
+  </si>
+  <si>
+    <t>max_return_10G_Top2_P60d</t>
+  </si>
+  <si>
+    <t>factor_score_10G_Top2_P30d</t>
+  </si>
+  <si>
+    <t>mvo_5G_Top3_P10d</t>
+  </si>
+  <si>
+    <t>max_return_5G_Top3_P30d</t>
+  </si>
+  <si>
+    <t>min_variance_10G_Top2_P30d</t>
+  </si>
+  <si>
+    <t>max_return_10G_Top3_P20d</t>
   </si>
   <si>
     <t>max_return_5G_Top2_P20d</t>
-  </si>
-  <si>
-    <t>min_variance_5G_Top2_P20d</t>
-  </si>
-  <si>
-    <t>mvo_5G_Top2_P20d</t>
-  </si>
-  <si>
-    <t>equal_5G_Top2_P30d</t>
-  </si>
-  <si>
-    <t>factor_score_5G_Top2_P30d</t>
-  </si>
-  <si>
-    <t>max_return_5G_Top2_P30d</t>
-  </si>
-  <si>
-    <t>min_variance_5G_Top2_P30d</t>
-  </si>
-  <si>
-    <t>mvo_5G_Top2_P30d</t>
-  </si>
-  <si>
-    <t>equal_5G_Top2_P60d</t>
-  </si>
-  <si>
-    <t>factor_score_5G_Top2_P60d</t>
-  </si>
-  <si>
-    <t>max_return_5G_Top2_P60d</t>
-  </si>
-  <si>
-    <t>min_variance_5G_Top2_P60d</t>
-  </si>
-  <si>
-    <t>mvo_5G_Top2_P60d</t>
-  </si>
-  <si>
-    <t>equal_5G_Top3_P10d</t>
-  </si>
-  <si>
-    <t>factor_score_5G_Top3_P10d</t>
-  </si>
-  <si>
-    <t>max_return_5G_Top3_P10d</t>
-  </si>
-  <si>
-    <t>min_variance_5G_Top3_P10d</t>
-  </si>
-  <si>
-    <t>mvo_5G_Top3_P10d</t>
-  </si>
-  <si>
-    <t>equal_5G_Top3_P20d</t>
-  </si>
-  <si>
-    <t>factor_score_5G_Top3_P20d</t>
-  </si>
-  <si>
-    <t>max_return_5G_Top3_P20d</t>
-  </si>
-  <si>
-    <t>min_variance_5G_Top3_P20d</t>
-  </si>
-  <si>
-    <t>mvo_5G_Top3_P20d</t>
-  </si>
-  <si>
-    <t>equal_5G_Top3_P30d</t>
-  </si>
-  <si>
-    <t>factor_score_5G_Top3_P30d</t>
-  </si>
-  <si>
-    <t>max_return_5G_Top3_P30d</t>
-  </si>
-  <si>
-    <t>min_variance_5G_Top3_P30d</t>
-  </si>
-  <si>
-    <t>mvo_5G_Top3_P30d</t>
-  </si>
-  <si>
-    <t>equal_5G_Top3_P60d</t>
-  </si>
-  <si>
-    <t>factor_score_5G_Top3_P60d</t>
-  </si>
-  <si>
-    <t>max_return_5G_Top3_P60d</t>
-  </si>
-  <si>
-    <t>min_variance_5G_Top3_P60d</t>
-  </si>
-  <si>
-    <t>mvo_5G_Top3_P60d</t>
-  </si>
-  <si>
-    <t>equal_10G_Top1_P10d</t>
-  </si>
-  <si>
-    <t>factor_score_10G_Top1_P10d</t>
-  </si>
-  <si>
-    <t>max_return_10G_Top1_P10d</t>
-  </si>
-  <si>
-    <t>min_variance_10G_Top1_P10d</t>
-  </si>
-  <si>
-    <t>mvo_10G_Top1_P10d</t>
-  </si>
-  <si>
-    <t>equal_10G_Top1_P20d</t>
-  </si>
-  <si>
-    <t>factor_score_10G_Top1_P20d</t>
-  </si>
-  <si>
-    <t>max_return_10G_Top1_P20d</t>
-  </si>
-  <si>
-    <t>min_variance_10G_Top1_P20d</t>
-  </si>
-  <si>
-    <t>mvo_10G_Top1_P20d</t>
-  </si>
-  <si>
-    <t>equal_10G_Top1_P30d</t>
-  </si>
-  <si>
-    <t>factor_score_10G_Top1_P30d</t>
-  </si>
-  <si>
-    <t>max_return_10G_Top1_P30d</t>
-  </si>
-  <si>
-    <t>min_variance_10G_Top1_P30d</t>
-  </si>
-  <si>
-    <t>mvo_10G_Top1_P30d</t>
-  </si>
-  <si>
-    <t>equal_10G_Top1_P60d</t>
-  </si>
-  <si>
-    <t>factor_score_10G_Top1_P60d</t>
-  </si>
-  <si>
-    <t>max_return_10G_Top1_P60d</t>
-  </si>
-  <si>
-    <t>min_variance_10G_Top1_P60d</t>
-  </si>
-  <si>
-    <t>mvo_10G_Top1_P60d</t>
-  </si>
-  <si>
-    <t>equal_10G_Top2_P10d</t>
-  </si>
-  <si>
-    <t>factor_score_10G_Top2_P10d</t>
-  </si>
-  <si>
-    <t>max_return_10G_Top2_P10d</t>
-  </si>
-  <si>
-    <t>min_variance_10G_Top2_P10d</t>
-  </si>
-  <si>
-    <t>mvo_10G_Top2_P10d</t>
-  </si>
-  <si>
-    <t>equal_10G_Top2_P20d</t>
-  </si>
-  <si>
-    <t>factor_score_10G_Top2_P20d</t>
-  </si>
-  <si>
-    <t>max_return_10G_Top2_P20d</t>
-  </si>
-  <si>
-    <t>min_variance_10G_Top2_P20d</t>
-  </si>
-  <si>
-    <t>mvo_10G_Top2_P20d</t>
-  </si>
-  <si>
-    <t>equal_10G_Top2_P30d</t>
-  </si>
-  <si>
-    <t>factor_score_10G_Top2_P30d</t>
-  </si>
-  <si>
-    <t>max_return_10G_Top2_P30d</t>
-  </si>
-  <si>
-    <t>min_variance_10G_Top2_P30d</t>
-  </si>
-  <si>
-    <t>mvo_10G_Top2_P30d</t>
-  </si>
-  <si>
-    <t>equal_10G_Top2_P60d</t>
-  </si>
-  <si>
-    <t>factor_score_10G_Top2_P60d</t>
-  </si>
-  <si>
-    <t>max_return_10G_Top2_P60d</t>
-  </si>
-  <si>
-    <t>min_variance_10G_Top2_P60d</t>
-  </si>
-  <si>
-    <t>mvo_10G_Top2_P60d</t>
-  </si>
-  <si>
-    <t>equal_10G_Top3_P10d</t>
-  </si>
-  <si>
-    <t>factor_score_10G_Top3_P10d</t>
-  </si>
-  <si>
-    <t>max_return_10G_Top3_P10d</t>
-  </si>
-  <si>
-    <t>min_variance_10G_Top3_P10d</t>
-  </si>
-  <si>
-    <t>mvo_10G_Top3_P10d</t>
-  </si>
-  <si>
-    <t>equal_10G_Top3_P20d</t>
-  </si>
-  <si>
-    <t>factor_score_10G_Top3_P20d</t>
-  </si>
-  <si>
-    <t>max_return_10G_Top3_P20d</t>
-  </si>
-  <si>
-    <t>min_variance_10G_Top3_P20d</t>
-  </si>
-  <si>
-    <t>mvo_10G_Top3_P20d</t>
-  </si>
-  <si>
-    <t>equal_10G_Top3_P30d</t>
-  </si>
-  <si>
-    <t>factor_score_10G_Top3_P30d</t>
-  </si>
-  <si>
-    <t>max_return_10G_Top3_P30d</t>
-  </si>
-  <si>
-    <t>min_variance_10G_Top3_P30d</t>
-  </si>
-  <si>
-    <t>mvo_10G_Top3_P30d</t>
-  </si>
-  <si>
-    <t>equal_10G_Top3_P60d</t>
-  </si>
-  <si>
-    <t>factor_score_10G_Top3_P60d</t>
-  </si>
-  <si>
-    <t>max_return_10G_Top3_P60d</t>
-  </si>
-  <si>
-    <t>min_variance_10G_Top3_P60d</t>
-  </si>
-  <si>
-    <t>mvo_10G_Top3_P60d</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -468,13 +484,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -512,7 +536,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -546,6 +570,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -580,9 +605,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -755,11 +781,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L121"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="16.08984375" customWidth="1"/>
+    <col min="5" max="5" width="25.453125" customWidth="1"/>
+    <col min="6" max="6" width="17.26953125" customWidth="1"/>
+    <col min="7" max="7" width="15.1796875" customWidth="1"/>
+    <col min="9" max="9" width="20.54296875" customWidth="1"/>
+    <col min="10" max="10" width="20.1796875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -797,127 +831,202 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>5</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="F2">
+        <v>1.7687318265156959</v>
+      </c>
+      <c r="G2">
+        <v>2.2017557032044568</v>
+      </c>
+      <c r="H2">
+        <v>0.75</v>
+      </c>
+      <c r="I2">
+        <v>0.31830678960861192</v>
+      </c>
+      <c r="J2">
+        <v>-4.4659967811070928E-2</v>
       </c>
       <c r="K2">
         <v>12</v>
       </c>
       <c r="L2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+        <v>1.026191322194558</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>5</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3">
+        <v>1.7687318265156959</v>
+      </c>
+      <c r="G3">
+        <v>2.2017557032044568</v>
+      </c>
+      <c r="H3">
+        <v>0.75</v>
+      </c>
+      <c r="I3">
+        <v>0.31830678960861192</v>
+      </c>
+      <c r="J3">
+        <v>-4.4659967811070928E-2</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
+        <v>1.026191322194558</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>60</v>
+      </c>
+      <c r="D4" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4">
+        <v>1.7687318265156959</v>
+      </c>
+      <c r="G4">
+        <v>2.2017557032044568</v>
+      </c>
+      <c r="H4">
+        <v>0.75</v>
+      </c>
+      <c r="I4">
+        <v>0.31830678960861192</v>
+      </c>
+      <c r="J4">
+        <v>-4.4659967811070928E-2</v>
+      </c>
+      <c r="K4">
+        <v>12</v>
+      </c>
+      <c r="L4">
+        <v>1.026191322194558</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>60</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5">
+        <v>1.7687318265156959</v>
+      </c>
+      <c r="G5">
+        <v>2.2017557032044568</v>
+      </c>
+      <c r="H5">
+        <v>0.75</v>
+      </c>
+      <c r="I5">
+        <v>0.31830678960861192</v>
+      </c>
+      <c r="J5">
+        <v>-4.4659967811070928E-2</v>
+      </c>
+      <c r="K5">
+        <v>12</v>
+      </c>
+      <c r="L5">
+        <v>1.026191322194558</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
         <v>18</v>
       </c>
-      <c r="K3">
-        <v>12</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4">
-        <v>12</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5">
-        <v>12</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
+      <c r="F6">
+        <v>1.7679079601552989</v>
+      </c>
+      <c r="G6">
+        <v>2.0154564135535789</v>
+      </c>
+      <c r="H6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I6">
+        <v>0.29052912108339091</v>
+      </c>
+      <c r="J6">
+        <v>-4.4230471707584873E-2</v>
       </c>
       <c r="K6">
         <v>12</v>
       </c>
       <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+        <v>1.0566506111234391</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7">
         <v>20</v>
@@ -926,185 +1035,305 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>17</v>
+      </c>
+      <c r="F7">
+        <v>1.7571973605785061</v>
+      </c>
+      <c r="G7">
+        <v>1.6695887252981321</v>
+      </c>
+      <c r="H7">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="I7">
+        <v>0.24062174483243051</v>
+      </c>
+      <c r="J7">
+        <v>-5.6341516836441417E-2</v>
       </c>
       <c r="K7">
         <v>12</v>
       </c>
       <c r="L7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+        <v>1.0902558048156099</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8">
+        <v>1.71400434264802</v>
+      </c>
+      <c r="G8">
+        <v>2.2197696670847131</v>
+      </c>
+      <c r="H8">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I8">
+        <v>0.31876797756846398</v>
+      </c>
+      <c r="J8">
+        <v>-4.8968363125061552E-2</v>
+      </c>
+      <c r="K8">
+        <v>12</v>
+      </c>
+      <c r="L8">
+        <v>1.0287761038677601</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9">
+        <v>1.7023435495562049</v>
+      </c>
+      <c r="G9">
+        <v>2.5911865067057049</v>
+      </c>
+      <c r="H9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I9">
+        <v>0.59647315596609418</v>
+      </c>
+      <c r="J9">
+        <v>-5.6988317331250843E-2</v>
+      </c>
+      <c r="K9">
+        <v>12</v>
+      </c>
+      <c r="L9">
+        <v>0.96447526990067201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
         <v>13</v>
       </c>
-      <c r="E8" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8">
-        <v>12</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9">
-        <v>5</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>20</v>
-      </c>
-      <c r="D9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9">
-        <v>12</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10">
-        <v>5</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>20</v>
-      </c>
-      <c r="D10" t="s">
-        <v>15</v>
-      </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>19</v>
+      </c>
+      <c r="F10">
+        <v>1.6863932918841911</v>
+      </c>
+      <c r="G10">
+        <v>1.937270247711216</v>
+      </c>
+      <c r="H10">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="I10">
+        <v>0.36234144278041552</v>
+      </c>
+      <c r="J10">
+        <v>-6.1387955557353761E-2</v>
       </c>
       <c r="K10">
         <v>12</v>
       </c>
       <c r="L10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+        <v>1.051692964719255</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>5</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11">
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="F11">
+        <v>1.659298582350115</v>
+      </c>
+      <c r="G11">
+        <v>1.8327752881695101</v>
+      </c>
+      <c r="H11">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="I11">
+        <v>0.23452362597472931</v>
+      </c>
+      <c r="J11">
+        <v>-5.9660654141002321E-2</v>
       </c>
       <c r="K11">
         <v>12</v>
       </c>
       <c r="L11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+        <v>1.0446226442723701</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12">
         <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>27</v>
+        <v>32</v>
+      </c>
+      <c r="F12">
+        <v>1.639167966134901</v>
+      </c>
+      <c r="G12">
+        <v>2.1601989659817158</v>
+      </c>
+      <c r="H12">
+        <v>0.75</v>
+      </c>
+      <c r="I12">
+        <v>0.3889558622168568</v>
+      </c>
+      <c r="J12">
+        <v>-6.076448425627478E-2</v>
       </c>
       <c r="K12">
         <v>12</v>
       </c>
       <c r="L12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+        <v>0.97559791810389163</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C13">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" t="s">
         <v>28</v>
       </c>
+      <c r="F13">
+        <v>1.6118747309127071</v>
+      </c>
+      <c r="G13">
+        <v>2.625324523169454</v>
+      </c>
+      <c r="H13">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I13">
+        <v>0.34635782745806909</v>
+      </c>
+      <c r="J13">
+        <v>-5.0315268243672197E-2</v>
+      </c>
       <c r="K13">
         <v>12</v>
       </c>
       <c r="L13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+        <v>0.97750110486556363</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
         <v>29</v>
       </c>
+      <c r="F14">
+        <v>1.6118747309127071</v>
+      </c>
+      <c r="G14">
+        <v>2.625324523169454</v>
+      </c>
+      <c r="H14">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I14">
+        <v>0.34635782745806909</v>
+      </c>
+      <c r="J14">
+        <v>-5.0315268243672197E-2</v>
+      </c>
       <c r="K14">
         <v>12</v>
       </c>
       <c r="L14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+        <v>0.97750110486556363</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
@@ -1112,152 +1341,257 @@
       <c r="E15" t="s">
         <v>30</v>
       </c>
+      <c r="F15">
+        <v>1.6118747309127071</v>
+      </c>
+      <c r="G15">
+        <v>2.625324523169454</v>
+      </c>
+      <c r="H15">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I15">
+        <v>0.34635782745806909</v>
+      </c>
+      <c r="J15">
+        <v>-5.0315268243672197E-2</v>
+      </c>
       <c r="K15">
         <v>12</v>
       </c>
       <c r="L15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+        <v>0.97750110486556363</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E16" t="s">
         <v>31</v>
       </c>
+      <c r="F16">
+        <v>1.6118747309127071</v>
+      </c>
+      <c r="G16">
+        <v>2.625324523169454</v>
+      </c>
+      <c r="H16">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I16">
+        <v>0.34635782745806909</v>
+      </c>
+      <c r="J16">
+        <v>-5.0315268243672197E-2</v>
+      </c>
       <c r="K16">
         <v>12</v>
       </c>
       <c r="L16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+        <v>0.97750110486556363</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>5</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17">
         <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
+        <v>27</v>
+      </c>
+      <c r="F17">
+        <v>1.599731692784389</v>
+      </c>
+      <c r="G17">
+        <v>2.277297161494753</v>
+      </c>
+      <c r="H17">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I17">
+        <v>0.30790578641061211</v>
+      </c>
+      <c r="J17">
+        <v>-4.735937710165683E-2</v>
       </c>
       <c r="K17">
         <v>12</v>
       </c>
       <c r="L17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+        <v>0.98143152306423143</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E18" t="s">
         <v>33</v>
       </c>
+      <c r="F18">
+        <v>1.587122048546473</v>
+      </c>
+      <c r="G18">
+        <v>1.701848396729039</v>
+      </c>
+      <c r="H18">
+        <v>0.75</v>
+      </c>
+      <c r="I18">
+        <v>0.3177625617971635</v>
+      </c>
+      <c r="J18">
+        <v>-5.5400797896680121E-2</v>
+      </c>
       <c r="K18">
         <v>12</v>
       </c>
       <c r="L18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+        <v>0.97088391685899</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>5</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E19" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="F19">
+        <v>1.5691245201263679</v>
+      </c>
+      <c r="G19">
+        <v>1.8467254110552449</v>
+      </c>
+      <c r="H19">
+        <v>0.75</v>
+      </c>
+      <c r="I19">
+        <v>0.20613206689361929</v>
+      </c>
+      <c r="J19">
+        <v>-5.2938595404275181E-2</v>
       </c>
       <c r="K19">
         <v>12</v>
       </c>
       <c r="L19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+        <v>0.95803405018185772</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C20">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>35</v>
+        <v>26</v>
+      </c>
+      <c r="F20">
+        <v>1.567441294999911</v>
+      </c>
+      <c r="G20">
+        <v>1.7305424423228879</v>
+      </c>
+      <c r="H20">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I20">
+        <v>0.35508765283829741</v>
+      </c>
+      <c r="J20">
+        <v>-5.5538944851506407E-2</v>
       </c>
       <c r="K20">
         <v>12</v>
       </c>
       <c r="L20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+        <v>0.98684479741216369</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C21">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="F21">
+        <v>1.486009715357163</v>
+      </c>
+      <c r="G21">
+        <v>2.0082139238944312</v>
+      </c>
+      <c r="H21">
+        <v>0.75</v>
+      </c>
+      <c r="I21">
+        <v>0.29481009882495718</v>
+      </c>
+      <c r="J21">
+        <v>-5.0547681570143443E-2</v>
       </c>
       <c r="K21">
         <v>12</v>
       </c>
       <c r="L21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
+        <v>0.91913083628330605</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>5</v>
       </c>
@@ -1265,142 +1599,232 @@
         <v>2</v>
       </c>
       <c r="C22">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E22" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="F22">
+        <v>1.407809566226393</v>
+      </c>
+      <c r="G22">
+        <v>1.743635742431235</v>
+      </c>
+      <c r="H22">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I22">
+        <v>0.3179316151983001</v>
+      </c>
+      <c r="J22">
+        <v>-4.8211641813192409E-2</v>
       </c>
       <c r="K22">
         <v>12</v>
       </c>
       <c r="L22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
+        <v>0.92246778762956727</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23">
         <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E23" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23">
+        <v>1.4056195997995611</v>
+      </c>
+      <c r="G23">
+        <v>2.5526864370763511</v>
+      </c>
+      <c r="H23">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I23">
+        <v>0.32695732400205513</v>
+      </c>
+      <c r="J23">
+        <v>-6.9665107278868432E-2</v>
+      </c>
+      <c r="K23">
+        <v>12</v>
+      </c>
+      <c r="L23">
+        <v>0.84669098043151059</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>10</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>60</v>
+      </c>
+      <c r="D24" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" t="s">
         <v>38</v>
       </c>
-      <c r="K23">
-        <v>12</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24">
-        <v>5</v>
-      </c>
-      <c r="B24">
-        <v>2</v>
-      </c>
-      <c r="C24">
-        <v>10</v>
-      </c>
-      <c r="D24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" t="s">
-        <v>39</v>
+      <c r="F24">
+        <v>1.389099058353952</v>
+      </c>
+      <c r="G24">
+        <v>1.744612789662729</v>
+      </c>
+      <c r="H24">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I24">
+        <v>0.2665922842182904</v>
+      </c>
+      <c r="J24">
+        <v>-4.7008372917454147E-2</v>
       </c>
       <c r="K24">
         <v>12</v>
       </c>
       <c r="L24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
+        <v>0.91494465942168479</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
         <v>15</v>
       </c>
       <c r="E25" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25">
+        <v>1.389099058353952</v>
+      </c>
+      <c r="G25">
+        <v>1.744612789662729</v>
+      </c>
+      <c r="H25">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I25">
+        <v>0.2665922842182904</v>
+      </c>
+      <c r="J25">
+        <v>-4.7008372917454147E-2</v>
+      </c>
+      <c r="K25">
+        <v>12</v>
+      </c>
+      <c r="L25">
+        <v>0.91494465942168479</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>10</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>60</v>
+      </c>
+      <c r="D26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s">
         <v>40</v>
       </c>
-      <c r="K25">
-        <v>12</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26">
-        <v>5</v>
-      </c>
-      <c r="B26">
-        <v>2</v>
-      </c>
-      <c r="C26">
-        <v>10</v>
-      </c>
-      <c r="D26" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="F26">
+        <v>1.389099058353952</v>
+      </c>
+      <c r="G26">
+        <v>1.744612789662729</v>
+      </c>
+      <c r="H26">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I26">
+        <v>0.2665922842182904</v>
+      </c>
+      <c r="J26">
+        <v>-4.7008372917454147E-2</v>
+      </c>
+      <c r="K26">
+        <v>12</v>
+      </c>
+      <c r="L26">
+        <v>0.91494465942168479</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>10</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>60</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
         <v>41</v>
       </c>
-      <c r="K26">
-        <v>12</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27">
-        <v>5</v>
-      </c>
-      <c r="B27">
-        <v>2</v>
-      </c>
-      <c r="C27">
-        <v>20</v>
-      </c>
-      <c r="D27" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" t="s">
-        <v>42</v>
+      <c r="F27">
+        <v>1.389099058353952</v>
+      </c>
+      <c r="G27">
+        <v>1.744612789662729</v>
+      </c>
+      <c r="H27">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I27">
+        <v>0.2665922842182904</v>
+      </c>
+      <c r="J27">
+        <v>-4.7008372917454147E-2</v>
       </c>
       <c r="K27">
         <v>12</v>
       </c>
       <c r="L27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
+        <v>0.91494465942168479</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>5</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28">
         <v>20</v>
@@ -1411,39 +1835,69 @@
       <c r="E28" t="s">
         <v>43</v>
       </c>
+      <c r="F28">
+        <v>1.37918992241795</v>
+      </c>
+      <c r="G28">
+        <v>1.9314021102549579</v>
+      </c>
+      <c r="H28">
+        <v>0.75</v>
+      </c>
+      <c r="I28">
+        <v>0.20073860320106321</v>
+      </c>
+      <c r="J28">
+        <v>-5.9092411200055248E-2</v>
+      </c>
       <c r="K28">
         <v>12</v>
       </c>
       <c r="L28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
+        <v>0.87901607404880866</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D29" t="s">
         <v>14</v>
       </c>
       <c r="E29" t="s">
-        <v>44</v>
+        <v>58</v>
+      </c>
+      <c r="F29">
+        <v>1.371356895315107</v>
+      </c>
+      <c r="G29">
+        <v>2.615353426721561</v>
+      </c>
+      <c r="H29">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I29">
+        <v>0.39218177326956227</v>
+      </c>
+      <c r="J29">
+        <v>-5.5313902004863198E-2</v>
       </c>
       <c r="K29">
         <v>12</v>
       </c>
       <c r="L29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
+        <v>0.83152219736500066</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -1452,19 +1906,34 @@
         <v>20</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>45</v>
+        <v>42</v>
+      </c>
+      <c r="F30">
+        <v>1.359985990350034</v>
+      </c>
+      <c r="G30">
+        <v>1.5867516892880029</v>
+      </c>
+      <c r="H30">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I30">
+        <v>0.21475535472421151</v>
+      </c>
+      <c r="J30">
+        <v>-6.4773639181015905E-2</v>
       </c>
       <c r="K30">
         <v>12</v>
       </c>
       <c r="L30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
+        <v>0.90996996551620457</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>5</v>
       </c>
@@ -1472,22 +1941,37 @@
         <v>2</v>
       </c>
       <c r="C31">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E31" t="s">
-        <v>46</v>
+        <v>69</v>
+      </c>
+      <c r="F31">
+        <v>1.343003516885201</v>
+      </c>
+      <c r="G31">
+        <v>2.265914158355459</v>
+      </c>
+      <c r="H31">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I31">
+        <v>0.29448315242434359</v>
+      </c>
+      <c r="J31">
+        <v>-6.0087728831143501E-2</v>
       </c>
       <c r="K31">
         <v>12</v>
       </c>
       <c r="L31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
+        <v>0.8040593018039196</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>5</v>
       </c>
@@ -1495,22 +1979,37 @@
         <v>2</v>
       </c>
       <c r="C32">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D32" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E32" t="s">
-        <v>47</v>
+        <v>52</v>
+      </c>
+      <c r="F32">
+        <v>1.3088936222592169</v>
+      </c>
+      <c r="G32">
+        <v>2.1232587928179489</v>
+      </c>
+      <c r="H32">
+        <v>0.75</v>
+      </c>
+      <c r="I32">
+        <v>0.23760072641027699</v>
+      </c>
+      <c r="J32">
+        <v>-4.8590391547235608E-2</v>
       </c>
       <c r="K32">
         <v>12</v>
       </c>
       <c r="L32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12">
+        <v>0.84461096860876572</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>5</v>
       </c>
@@ -1518,22 +2017,37 @@
         <v>2</v>
       </c>
       <c r="C33">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>48</v>
+        <v>53</v>
+      </c>
+      <c r="F33">
+        <v>1.3088936222592169</v>
+      </c>
+      <c r="G33">
+        <v>2.1232587928179489</v>
+      </c>
+      <c r="H33">
+        <v>0.75</v>
+      </c>
+      <c r="I33">
+        <v>0.23760072641027699</v>
+      </c>
+      <c r="J33">
+        <v>-4.8590391547235608E-2</v>
       </c>
       <c r="K33">
         <v>12</v>
       </c>
       <c r="L33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12">
+        <v>0.84461096860876572</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>5</v>
       </c>
@@ -1541,22 +2055,37 @@
         <v>2</v>
       </c>
       <c r="C34">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D34" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E34" t="s">
-        <v>49</v>
+        <v>54</v>
+      </c>
+      <c r="F34">
+        <v>1.3088936222592169</v>
+      </c>
+      <c r="G34">
+        <v>2.1232587928179489</v>
+      </c>
+      <c r="H34">
+        <v>0.75</v>
+      </c>
+      <c r="I34">
+        <v>0.23760072641027699</v>
+      </c>
+      <c r="J34">
+        <v>-4.8590391547235608E-2</v>
       </c>
       <c r="K34">
         <v>12</v>
       </c>
       <c r="L34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12">
+        <v>0.84461096860876572</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>5</v>
       </c>
@@ -1564,22 +2093,37 @@
         <v>2</v>
       </c>
       <c r="C35">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D35" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E35" t="s">
-        <v>50</v>
+        <v>55</v>
+      </c>
+      <c r="F35">
+        <v>1.3088936222592169</v>
+      </c>
+      <c r="G35">
+        <v>2.1232587928179489</v>
+      </c>
+      <c r="H35">
+        <v>0.75</v>
+      </c>
+      <c r="I35">
+        <v>0.23760072641027699</v>
+      </c>
+      <c r="J35">
+        <v>-4.8590391547235608E-2</v>
       </c>
       <c r="K35">
         <v>12</v>
       </c>
       <c r="L35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12">
+        <v>0.84461096860876572</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>5</v>
       </c>
@@ -1587,22 +2131,37 @@
         <v>2</v>
       </c>
       <c r="C36">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E36" t="s">
-        <v>51</v>
+        <v>63</v>
+      </c>
+      <c r="F36">
+        <v>1.3075519377049469</v>
+      </c>
+      <c r="G36">
+        <v>2.5434124012429851</v>
+      </c>
+      <c r="H36">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I36">
+        <v>0.28559581236652398</v>
+      </c>
+      <c r="J36">
+        <v>-5.3872095994294537E-2</v>
       </c>
       <c r="K36">
         <v>12</v>
       </c>
       <c r="L36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12">
+        <v>0.80768492534988534</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>5</v>
       </c>
@@ -1610,50 +2169,80 @@
         <v>2</v>
       </c>
       <c r="C37">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="D37" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E37" t="s">
-        <v>52</v>
+        <v>62</v>
+      </c>
+      <c r="F37">
+        <v>1.2997280605121351</v>
+      </c>
+      <c r="G37">
+        <v>2.1997171004299561</v>
+      </c>
+      <c r="H37">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I37">
+        <v>0.25666873191851219</v>
+      </c>
+      <c r="J37">
+        <v>-6.559642450042083E-2</v>
       </c>
       <c r="K37">
         <v>12</v>
       </c>
       <c r="L37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12">
+        <v>0.8136495130109761</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="D38" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E38" t="s">
-        <v>53</v>
+        <v>44</v>
+      </c>
+      <c r="F38">
+        <v>1.2825730225843319</v>
+      </c>
+      <c r="G38">
+        <v>1.8374884209504421</v>
+      </c>
+      <c r="H38">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I38">
+        <v>0.3222910269225549</v>
+      </c>
+      <c r="J38">
+        <v>-6.8493985354250345E-2</v>
       </c>
       <c r="K38">
         <v>12</v>
       </c>
       <c r="L38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12">
+        <v>0.86875651272419596</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>5</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39">
         <v>60</v>
@@ -1662,116 +2251,191 @@
         <v>14</v>
       </c>
       <c r="E39" t="s">
-        <v>54</v>
+        <v>56</v>
+      </c>
+      <c r="F39">
+        <v>1.2576451542786391</v>
+      </c>
+      <c r="G39">
+        <v>1.685819188633364</v>
+      </c>
+      <c r="H39">
+        <v>0.75</v>
+      </c>
+      <c r="I39">
+        <v>0.25418085671171731</v>
+      </c>
+      <c r="J39">
+        <v>-4.852710429348784E-2</v>
       </c>
       <c r="K39">
         <v>12</v>
       </c>
       <c r="L39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12">
+        <v>0.83975582650129244</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B40">
         <v>2</v>
       </c>
       <c r="C40">
+        <v>20</v>
+      </c>
+      <c r="D40" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" t="s">
+        <v>47</v>
+      </c>
+      <c r="F40">
+        <v>1.2439139798373069</v>
+      </c>
+      <c r="G40">
+        <v>1.611250442113757</v>
+      </c>
+      <c r="H40">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I40">
+        <v>0.22905519332868121</v>
+      </c>
+      <c r="J40">
+        <v>-7.0995374056315175E-2</v>
+      </c>
+      <c r="K40">
+        <v>12</v>
+      </c>
+      <c r="L40">
+        <v>0.86245307846691377</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>10</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41">
+        <v>10</v>
+      </c>
+      <c r="D41" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" t="s">
+        <v>50</v>
+      </c>
+      <c r="F41">
+        <v>1.221086656317945</v>
+      </c>
+      <c r="G41">
+        <v>1.648967977424475</v>
+      </c>
+      <c r="H41">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I41">
+        <v>0.25770321875552088</v>
+      </c>
+      <c r="J41">
+        <v>-6.541324253578272E-2</v>
+      </c>
+      <c r="K41">
+        <v>12</v>
+      </c>
+      <c r="L41">
+        <v>0.85168631470142675</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>5</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>10</v>
+      </c>
+      <c r="D42" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" t="s">
+        <v>45</v>
+      </c>
+      <c r="F42">
+        <v>1.219398340225694</v>
+      </c>
+      <c r="G42">
+        <v>1.373497850541143</v>
+      </c>
+      <c r="H42">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I42">
+        <v>0.25774588856441483</v>
+      </c>
+      <c r="J42">
+        <v>-6.240928068941199E-2</v>
+      </c>
+      <c r="K42">
+        <v>12</v>
+      </c>
+      <c r="L42">
+        <v>0.86415506884040505</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>10</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43">
+        <v>20</v>
+      </c>
+      <c r="D43" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" t="s">
+        <v>74</v>
+      </c>
+      <c r="F43">
+        <v>1.216021655750485</v>
+      </c>
+      <c r="G43">
+        <v>2.0497223266892859</v>
+      </c>
+      <c r="H43">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I43">
+        <v>0.28864766589982982</v>
+      </c>
+      <c r="J43">
+        <v>-6.2279534456091169E-2</v>
+      </c>
+      <c r="K43">
+        <v>12</v>
+      </c>
+      <c r="L43">
+        <v>0.78477827364958963</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>10</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
         <v>60</v>
-      </c>
-      <c r="D40" t="s">
-        <v>15</v>
-      </c>
-      <c r="E40" t="s">
-        <v>55</v>
-      </c>
-      <c r="K40">
-        <v>12</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12">
-      <c r="A41">
-        <v>5</v>
-      </c>
-      <c r="B41">
-        <v>2</v>
-      </c>
-      <c r="C41">
-        <v>60</v>
-      </c>
-      <c r="D41" t="s">
-        <v>16</v>
-      </c>
-      <c r="E41" t="s">
-        <v>56</v>
-      </c>
-      <c r="K41">
-        <v>12</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12">
-      <c r="A42">
-        <v>5</v>
-      </c>
-      <c r="B42">
-        <v>3</v>
-      </c>
-      <c r="C42">
-        <v>10</v>
-      </c>
-      <c r="D42" t="s">
-        <v>12</v>
-      </c>
-      <c r="E42" t="s">
-        <v>57</v>
-      </c>
-      <c r="K42">
-        <v>12</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12">
-      <c r="A43">
-        <v>5</v>
-      </c>
-      <c r="B43">
-        <v>3</v>
-      </c>
-      <c r="C43">
-        <v>10</v>
-      </c>
-      <c r="D43" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" t="s">
-        <v>58</v>
-      </c>
-      <c r="K43">
-        <v>12</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12">
-      <c r="A44">
-        <v>5</v>
-      </c>
-      <c r="B44">
-        <v>3</v>
-      </c>
-      <c r="C44">
-        <v>10</v>
       </c>
       <c r="D44" t="s">
         <v>14</v>
@@ -1779,16 +2443,31 @@
       <c r="E44" t="s">
         <v>59</v>
       </c>
+      <c r="F44">
+        <v>1.213265431921658</v>
+      </c>
+      <c r="G44">
+        <v>1.693735918177919</v>
+      </c>
+      <c r="H44">
+        <v>0.75</v>
+      </c>
+      <c r="I44">
+        <v>0.26122641939949148</v>
+      </c>
+      <c r="J44">
+        <v>-5.0662653424885379E-2</v>
+      </c>
       <c r="K44">
         <v>12</v>
       </c>
       <c r="L44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12">
+        <v>0.82167566447552798</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B45">
         <v>3</v>
@@ -1797,111 +2476,186 @@
         <v>10</v>
       </c>
       <c r="D45" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E45" t="s">
-        <v>60</v>
+        <v>68</v>
+      </c>
+      <c r="F45">
+        <v>1.211440969426486</v>
+      </c>
+      <c r="G45">
+        <v>2.1549966839454342</v>
+      </c>
+      <c r="H45">
+        <v>0.75</v>
+      </c>
+      <c r="I45">
+        <v>0.22985380469303779</v>
+      </c>
+      <c r="J45">
+        <v>-6.2664536993059697E-2</v>
       </c>
       <c r="K45">
         <v>12</v>
       </c>
       <c r="L45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12">
+        <v>0.8046636509447791</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C46">
         <v>10</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E46" t="s">
-        <v>61</v>
+        <v>46</v>
+      </c>
+      <c r="F46">
+        <v>1.2111601667598351</v>
+      </c>
+      <c r="G46">
+        <v>1.328911033864445</v>
+      </c>
+      <c r="H46">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I46">
+        <v>0.27733609436582951</v>
+      </c>
+      <c r="J46">
+        <v>-6.495226936207435E-2</v>
       </c>
       <c r="K46">
         <v>12</v>
       </c>
       <c r="L46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12">
+        <v>0.86327963571354083</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C47">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D47" t="s">
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>62</v>
+        <v>49</v>
+      </c>
+      <c r="F47">
+        <v>1.210052299974117</v>
+      </c>
+      <c r="G47">
+        <v>1.4995804484720769</v>
+      </c>
+      <c r="H47">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I47">
+        <v>0.2363799107331627</v>
+      </c>
+      <c r="J47">
+        <v>-6.0002895539734008E-2</v>
       </c>
       <c r="K47">
         <v>12</v>
       </c>
       <c r="L47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12">
+        <v>0.85404106184320538</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>5</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C48">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D48" t="s">
         <v>13</v>
       </c>
       <c r="E48" t="s">
-        <v>63</v>
+        <v>48</v>
+      </c>
+      <c r="F48">
+        <v>1.209592902665211</v>
+      </c>
+      <c r="G48">
+        <v>1.4547635584398491</v>
+      </c>
+      <c r="H48">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I48">
+        <v>0.2528105654301343</v>
+      </c>
+      <c r="J48">
+        <v>-6.1213565005426518E-2</v>
       </c>
       <c r="K48">
         <v>12</v>
       </c>
       <c r="L48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12">
+        <v>0.85604852393586228</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C49">
         <v>20</v>
       </c>
       <c r="D49" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E49" t="s">
-        <v>64</v>
+        <v>61</v>
+      </c>
+      <c r="F49">
+        <v>1.193123253163707</v>
+      </c>
+      <c r="G49">
+        <v>1.672309947556091</v>
+      </c>
+      <c r="H49">
+        <v>0.75</v>
+      </c>
+      <c r="I49">
+        <v>0.15782372269847711</v>
+      </c>
+      <c r="J49">
+        <v>-5.9529394660193982E-2</v>
       </c>
       <c r="K49">
         <v>12</v>
       </c>
       <c r="L49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12">
+        <v>0.81451172811247308</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>5</v>
       </c>
@@ -1909,168 +2663,273 @@
         <v>3</v>
       </c>
       <c r="C50">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E50" t="s">
-        <v>65</v>
+        <v>60</v>
+      </c>
+      <c r="F50">
+        <v>1.1914567454613649</v>
+      </c>
+      <c r="G50">
+        <v>1.6315304222363789</v>
+      </c>
+      <c r="H50">
+        <v>0.75</v>
+      </c>
+      <c r="I50">
+        <v>0.1774247744955928</v>
+      </c>
+      <c r="J50">
+        <v>-5.1332249093952842E-2</v>
       </c>
       <c r="K50">
         <v>12</v>
       </c>
       <c r="L50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12">
+        <v>0.81558480033202874</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>5</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C51">
         <v>20</v>
       </c>
       <c r="D51" t="s">
+        <v>14</v>
+      </c>
+      <c r="E51" t="s">
+        <v>78</v>
+      </c>
+      <c r="F51">
+        <v>1.183711637142655</v>
+      </c>
+      <c r="G51">
+        <v>2.046136524902558</v>
+      </c>
+      <c r="H51">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I51">
+        <v>0.25175516416669508</v>
+      </c>
+      <c r="J51">
+        <v>-5.9915363556220631E-2</v>
+      </c>
+      <c r="K51">
+        <v>12</v>
+      </c>
+      <c r="L51">
+        <v>0.77197006335647167</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>5</v>
+      </c>
+      <c r="B52">
+        <v>1</v>
+      </c>
+      <c r="C52">
+        <v>60</v>
+      </c>
+      <c r="D52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" t="s">
+        <v>64</v>
+      </c>
+      <c r="F52">
+        <v>1.182471550526857</v>
+      </c>
+      <c r="G52">
+        <v>1.76206803402622</v>
+      </c>
+      <c r="H52">
+        <v>0.75</v>
+      </c>
+      <c r="I52">
+        <v>0.2119501916386366</v>
+      </c>
+      <c r="J52">
+        <v>-4.5623761070159641E-2</v>
+      </c>
+      <c r="K52">
+        <v>12</v>
+      </c>
+      <c r="L52">
+        <v>0.80660288904998478</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>5</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <v>60</v>
+      </c>
+      <c r="D53" t="s">
         <v>16</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E53" t="s">
+        <v>65</v>
+      </c>
+      <c r="F53">
+        <v>1.182471550526857</v>
+      </c>
+      <c r="G53">
+        <v>1.76206803402622</v>
+      </c>
+      <c r="H53">
+        <v>0.75</v>
+      </c>
+      <c r="I53">
+        <v>0.2119501916386366</v>
+      </c>
+      <c r="J53">
+        <v>-4.5623761070159641E-2</v>
+      </c>
+      <c r="K53">
+        <v>12</v>
+      </c>
+      <c r="L53">
+        <v>0.80660288904998478</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>5</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54">
+        <v>60</v>
+      </c>
+      <c r="D54" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" t="s">
         <v>66</v>
       </c>
-      <c r="K51">
-        <v>12</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12">
-      <c r="A52">
-        <v>5</v>
-      </c>
-      <c r="B52">
-        <v>3</v>
-      </c>
-      <c r="C52">
-        <v>30</v>
-      </c>
-      <c r="D52" t="s">
-        <v>12</v>
-      </c>
-      <c r="E52" t="s">
-        <v>67</v>
-      </c>
-      <c r="K52">
-        <v>12</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12">
-      <c r="A53">
-        <v>5</v>
-      </c>
-      <c r="B53">
-        <v>3</v>
-      </c>
-      <c r="C53">
-        <v>30</v>
-      </c>
-      <c r="D53" t="s">
-        <v>13</v>
-      </c>
-      <c r="E53" t="s">
-        <v>68</v>
-      </c>
-      <c r="K53">
-        <v>12</v>
-      </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12">
-      <c r="A54">
-        <v>5</v>
-      </c>
-      <c r="B54">
-        <v>3</v>
-      </c>
-      <c r="C54">
-        <v>30</v>
-      </c>
-      <c r="D54" t="s">
-        <v>14</v>
-      </c>
-      <c r="E54" t="s">
-        <v>69</v>
+      <c r="F54">
+        <v>1.182471550526857</v>
+      </c>
+      <c r="G54">
+        <v>1.76206803402622</v>
+      </c>
+      <c r="H54">
+        <v>0.75</v>
+      </c>
+      <c r="I54">
+        <v>0.2119501916386366</v>
+      </c>
+      <c r="J54">
+        <v>-4.5623761070159641E-2</v>
       </c>
       <c r="K54">
         <v>12</v>
       </c>
       <c r="L54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12">
+        <v>0.80660288904998478</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>5</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D55" t="s">
         <v>15</v>
       </c>
       <c r="E55" t="s">
-        <v>70</v>
+        <v>67</v>
+      </c>
+      <c r="F55">
+        <v>1.182471550526857</v>
+      </c>
+      <c r="G55">
+        <v>1.76206803402622</v>
+      </c>
+      <c r="H55">
+        <v>0.75</v>
+      </c>
+      <c r="I55">
+        <v>0.2119501916386366</v>
+      </c>
+      <c r="J55">
+        <v>-4.5623761070159641E-2</v>
       </c>
       <c r="K55">
         <v>12</v>
       </c>
       <c r="L55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12">
+        <v>0.80660288904998478</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>5</v>
       </c>
       <c r="B56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D56" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E56" t="s">
         <v>71</v>
       </c>
+      <c r="F56">
+        <v>1.1761936301672209</v>
+      </c>
+      <c r="G56">
+        <v>1.943965913390088</v>
+      </c>
+      <c r="H56">
+        <v>0.75</v>
+      </c>
+      <c r="I56">
+        <v>0.17945190985968401</v>
+      </c>
+      <c r="J56">
+        <v>-5.8936431634782703E-2</v>
+      </c>
       <c r="K56">
         <v>12</v>
       </c>
       <c r="L56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12">
+        <v>0.7973808058508115</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>5</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="D57" t="s">
         <v>12</v>
@@ -2078,83 +2937,143 @@
       <c r="E57" t="s">
         <v>72</v>
       </c>
+      <c r="F57">
+        <v>1.169468924152459</v>
+      </c>
+      <c r="G57">
+        <v>1.894977598239711</v>
+      </c>
+      <c r="H57">
+        <v>0.75</v>
+      </c>
+      <c r="I57">
+        <v>0.2108846310613538</v>
+      </c>
+      <c r="J57">
+        <v>-5.9304639505500863E-2</v>
+      </c>
       <c r="K57">
         <v>12</v>
       </c>
       <c r="L57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12">
+        <v>0.79641531454661385</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>5</v>
       </c>
       <c r="B58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C58">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D58" t="s">
         <v>13</v>
       </c>
       <c r="E58" t="s">
-        <v>73</v>
+        <v>82</v>
+      </c>
+      <c r="F58">
+        <v>1.1596657196449629</v>
+      </c>
+      <c r="G58">
+        <v>2.067235220626316</v>
+      </c>
+      <c r="H58">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I58">
+        <v>0.26891375195073292</v>
+      </c>
+      <c r="J58">
+        <v>-5.9749697682129482E-2</v>
       </c>
       <c r="K58">
         <v>12</v>
       </c>
       <c r="L58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12">
+        <v>0.76167424141256812</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B59">
         <v>3</v>
       </c>
       <c r="C59">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="D59" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E59" t="s">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="F59">
+        <v>1.1560336655336261</v>
+      </c>
+      <c r="G59">
+        <v>2.0840388428616121</v>
+      </c>
+      <c r="H59">
+        <v>0.75</v>
+      </c>
+      <c r="I59">
+        <v>0.24566736159371741</v>
+      </c>
+      <c r="J59">
+        <v>-6.7701763053032424E-2</v>
       </c>
       <c r="K59">
         <v>12</v>
       </c>
       <c r="L59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12">
+        <v>0.78468850562950287</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>5</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C60">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="D60" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>75</v>
+        <v>57</v>
+      </c>
+      <c r="F60">
+        <v>1.1551177333005871</v>
+      </c>
+      <c r="G60">
+        <v>1.370003196035094</v>
+      </c>
+      <c r="H60">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I60">
+        <v>0.21294471540526741</v>
+      </c>
+      <c r="J60">
+        <v>-5.6402371908986643E-2</v>
       </c>
       <c r="K60">
         <v>12</v>
       </c>
       <c r="L60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12">
+        <v>0.83862920110046335</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>5</v>
       </c>
@@ -2162,22 +3081,37 @@
         <v>3</v>
       </c>
       <c r="C61">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="D61" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="F61">
+        <v>1.14860297787058</v>
+      </c>
+      <c r="G61">
+        <v>1.580294136399518</v>
+      </c>
+      <c r="H61">
+        <v>0.75</v>
+      </c>
+      <c r="I61">
+        <v>0.16433562768391291</v>
+      </c>
+      <c r="J61">
+        <v>-5.0450396996650333E-2</v>
       </c>
       <c r="K61">
         <v>12</v>
       </c>
       <c r="L61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12">
+        <v>0.80070700587376298</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>10</v>
       </c>
@@ -2185,73 +3119,118 @@
         <v>1</v>
       </c>
       <c r="C62">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D62" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E62" t="s">
-        <v>77</v>
+        <v>84</v>
+      </c>
+      <c r="F62">
+        <v>1.132743182509157</v>
+      </c>
+      <c r="G62">
+        <v>2.2690213682162739</v>
+      </c>
+      <c r="H62">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I62">
+        <v>0.28720041009243419</v>
+      </c>
+      <c r="J62">
+        <v>-5.4171050281982873E-2</v>
       </c>
       <c r="K62">
         <v>12</v>
       </c>
       <c r="L62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12">
+        <v>0.74486785698234559</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
       <c r="C63">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D63" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E63" t="s">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="F63">
+        <v>1.1250375390560969</v>
+      </c>
+      <c r="G63">
+        <v>2.2602744650120168</v>
+      </c>
+      <c r="H63">
+        <v>0.75</v>
+      </c>
+      <c r="I63">
+        <v>0.26486470305254051</v>
+      </c>
+      <c r="J63">
+        <v>-5.2382694176271588E-2</v>
       </c>
       <c r="K63">
         <v>12</v>
       </c>
       <c r="L63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12">
+        <v>0.76703180844754659</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D64" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E64" t="s">
-        <v>79</v>
+        <v>76</v>
+      </c>
+      <c r="F64">
+        <v>1.1159269726363521</v>
+      </c>
+      <c r="G64">
+        <v>1.887701156306228</v>
+      </c>
+      <c r="H64">
+        <v>0.75</v>
+      </c>
+      <c r="I64">
+        <v>0.1545179542502331</v>
+      </c>
+      <c r="J64">
+        <v>-5.3899759855279672E-2</v>
       </c>
       <c r="K64">
         <v>12</v>
       </c>
       <c r="L64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12">
+        <v>0.77525965558245458</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65">
         <v>10</v>
@@ -2260,16 +3239,31 @@
         <v>15</v>
       </c>
       <c r="E65" t="s">
-        <v>80</v>
+        <v>73</v>
+      </c>
+      <c r="F65">
+        <v>1.113093071096255</v>
+      </c>
+      <c r="G65">
+        <v>2.154791819410137</v>
+      </c>
+      <c r="H65">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I65">
+        <v>0.32756051176497653</v>
+      </c>
+      <c r="J65">
+        <v>-8.1442597313384948E-2</v>
       </c>
       <c r="K65">
         <v>12</v>
       </c>
       <c r="L65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12">
+        <v>0.79033066634911886</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>10</v>
       </c>
@@ -2277,47 +3271,77 @@
         <v>1</v>
       </c>
       <c r="C66">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D66" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E66" t="s">
         <v>81</v>
       </c>
+      <c r="F66">
+        <v>1.1094579224502421</v>
+      </c>
+      <c r="G66">
+        <v>2.2066009541392142</v>
+      </c>
+      <c r="H66">
+        <v>0.75</v>
+      </c>
+      <c r="I66">
+        <v>0.2463644948677268</v>
+      </c>
+      <c r="J66">
+        <v>-5.0115423336452997E-2</v>
+      </c>
       <c r="K66">
         <v>12</v>
       </c>
       <c r="L66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12">
+        <v>0.76234017974963064</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>10</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D67" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E67" t="s">
-        <v>82</v>
+        <v>77</v>
+      </c>
+      <c r="F67">
+        <v>1.0990974563757441</v>
+      </c>
+      <c r="G67">
+        <v>1.7864884002097761</v>
+      </c>
+      <c r="H67">
+        <v>0.75</v>
+      </c>
+      <c r="I67">
+        <v>0.28122543606612888</v>
+      </c>
+      <c r="J67">
+        <v>-6.2175662732871478E-2</v>
       </c>
       <c r="K67">
         <v>12</v>
       </c>
       <c r="L67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12">
+        <v>0.77230137223669126</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -2326,42 +3350,72 @@
         <v>20</v>
       </c>
       <c r="D68" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E68" t="s">
         <v>83</v>
       </c>
+      <c r="F68">
+        <v>1.0746345555023411</v>
+      </c>
+      <c r="G68">
+        <v>1.837559745515706</v>
+      </c>
+      <c r="H68">
+        <v>0.75</v>
+      </c>
+      <c r="I68">
+        <v>0.17197706212264149</v>
+      </c>
+      <c r="J68">
+        <v>-5.8725701239140969E-2</v>
+      </c>
       <c r="K68">
         <v>12</v>
       </c>
       <c r="L68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12">
+        <v>0.76057846834243192</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B69">
         <v>1</v>
       </c>
       <c r="C69">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D69" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E69" t="s">
-        <v>84</v>
+        <v>87</v>
+      </c>
+      <c r="F69">
+        <v>1.053534569264569</v>
+      </c>
+      <c r="G69">
+        <v>2.1675463819047871</v>
+      </c>
+      <c r="H69">
+        <v>0.75</v>
+      </c>
+      <c r="I69">
+        <v>0.21553074036851649</v>
+      </c>
+      <c r="J69">
+        <v>-4.904328050558019E-2</v>
       </c>
       <c r="K69">
         <v>12</v>
       </c>
       <c r="L69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12">
+        <v>0.74112435876981064</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>10</v>
       </c>
@@ -2369,114 +3423,189 @@
         <v>1</v>
       </c>
       <c r="C70">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D70" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E70" t="s">
-        <v>85</v>
+        <v>89</v>
+      </c>
+      <c r="F70">
+        <v>1.040485968788345</v>
+      </c>
+      <c r="G70">
+        <v>1.818409141453829</v>
+      </c>
+      <c r="H70">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I70">
+        <v>0.26261476367861331</v>
+      </c>
+      <c r="J70">
+        <v>-5.4399316994540592E-2</v>
       </c>
       <c r="K70">
         <v>12</v>
       </c>
       <c r="L70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12">
+        <v>0.72263741439441265</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B71">
         <v>1</v>
       </c>
       <c r="C71">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D71" t="s">
         <v>16</v>
       </c>
       <c r="E71" t="s">
-        <v>86</v>
+        <v>80</v>
+      </c>
+      <c r="F71">
+        <v>1.032303114005003</v>
+      </c>
+      <c r="G71">
+        <v>1.410302804449983</v>
+      </c>
+      <c r="H71">
+        <v>0.75</v>
+      </c>
+      <c r="I71">
+        <v>0.1428180274813495</v>
+      </c>
+      <c r="J71">
+        <v>-5.6060507432449579E-2</v>
       </c>
       <c r="K71">
         <v>12</v>
       </c>
       <c r="L71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12">
+        <v>0.7623869349112985</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D72" t="s">
         <v>12</v>
       </c>
       <c r="E72" t="s">
-        <v>87</v>
+        <v>90</v>
+      </c>
+      <c r="F72">
+        <v>1.0264828864547739</v>
+      </c>
+      <c r="G72">
+        <v>1.826167256382272</v>
+      </c>
+      <c r="H72">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I72">
+        <v>0.13851438905445959</v>
+      </c>
+      <c r="J72">
+        <v>-5.4666781976996308E-2</v>
       </c>
       <c r="K72">
         <v>12</v>
       </c>
       <c r="L72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12">
+        <v>0.71674398458764144</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C73">
         <v>30</v>
       </c>
       <c r="D73" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E73" t="s">
-        <v>88</v>
+        <v>91</v>
+      </c>
+      <c r="F73">
+        <v>1.017612988371509</v>
+      </c>
+      <c r="G73">
+        <v>1.8906921816549731</v>
+      </c>
+      <c r="H73">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I73">
+        <v>0.19402335532017931</v>
+      </c>
+      <c r="J73">
+        <v>-4.7520926125585609E-2</v>
       </c>
       <c r="K73">
         <v>12</v>
       </c>
       <c r="L73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12">
+        <v>0.71082656712657166</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>10</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C74">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D74" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E74" t="s">
-        <v>89</v>
+        <v>86</v>
+      </c>
+      <c r="F74">
+        <v>1.01126447639308</v>
+      </c>
+      <c r="G74">
+        <v>1.686634614415002</v>
+      </c>
+      <c r="H74">
+        <v>0.75</v>
+      </c>
+      <c r="I74">
+        <v>0.21050887445522909</v>
+      </c>
+      <c r="J74">
+        <v>-6.2162812017168632E-2</v>
       </c>
       <c r="K74">
         <v>12</v>
       </c>
       <c r="L74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12">
+        <v>0.74116965373772015</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>10</v>
       </c>
@@ -2484,24 +3613,39 @@
         <v>1</v>
       </c>
       <c r="C75">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D75" t="s">
         <v>15</v>
       </c>
       <c r="E75" t="s">
-        <v>90</v>
+        <v>94</v>
+      </c>
+      <c r="F75">
+        <v>0.99686622367056632</v>
+      </c>
+      <c r="G75">
+        <v>2.769610684110166</v>
+      </c>
+      <c r="H75">
+        <v>0.75</v>
+      </c>
+      <c r="I75">
+        <v>0.50760342591903773</v>
+      </c>
+      <c r="J75">
+        <v>-8.6152060654098098E-2</v>
       </c>
       <c r="K75">
         <v>12</v>
       </c>
       <c r="L75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12">
+        <v>0.70333030465226498</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B76">
         <v>1</v>
@@ -2510,42 +3654,72 @@
         <v>30</v>
       </c>
       <c r="D76" t="s">
+        <v>12</v>
+      </c>
+      <c r="E76" t="s">
+        <v>85</v>
+      </c>
+      <c r="F76">
+        <v>0.99151570404327627</v>
+      </c>
+      <c r="G76">
+        <v>2.1395007466854432</v>
+      </c>
+      <c r="H76">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I76">
+        <v>0.2017848216670452</v>
+      </c>
+      <c r="J76">
+        <v>-4.9535037531166469E-2</v>
+      </c>
+      <c r="K76">
+        <v>12</v>
+      </c>
+      <c r="L76">
+        <v>0.74216287618628074</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>10</v>
+      </c>
+      <c r="B77">
+        <v>3</v>
+      </c>
+      <c r="C77">
+        <v>30</v>
+      </c>
+      <c r="D77" t="s">
         <v>16</v>
       </c>
-      <c r="E76" t="s">
-        <v>91</v>
-      </c>
-      <c r="K76">
-        <v>12</v>
-      </c>
-      <c r="L76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12">
-      <c r="A77">
-        <v>10</v>
-      </c>
-      <c r="B77">
-        <v>1</v>
-      </c>
-      <c r="C77">
-        <v>60</v>
-      </c>
-      <c r="D77" t="s">
-        <v>12</v>
-      </c>
       <c r="E77" t="s">
-        <v>92</v>
+        <v>100</v>
+      </c>
+      <c r="F77">
+        <v>0.98945127587873649</v>
+      </c>
+      <c r="G77">
+        <v>1.879691874406993</v>
+      </c>
+      <c r="H77">
+        <v>0.5</v>
+      </c>
+      <c r="I77">
+        <v>0.21508092459393849</v>
+      </c>
+      <c r="J77">
+        <v>-5.5775858391880727E-2</v>
       </c>
       <c r="K77">
         <v>12</v>
       </c>
       <c r="L77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12">
+        <v>0.64995832279949417</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>10</v>
       </c>
@@ -2553,22 +3727,37 @@
         <v>1</v>
       </c>
       <c r="C78">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D78" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E78" t="s">
-        <v>93</v>
+        <v>95</v>
+      </c>
+      <c r="F78">
+        <v>0.98140163252940626</v>
+      </c>
+      <c r="G78">
+        <v>2.0308164020631709</v>
+      </c>
+      <c r="H78">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I78">
+        <v>0.17901886458229169</v>
+      </c>
+      <c r="J78">
+        <v>-5.9977785271709702E-2</v>
       </c>
       <c r="K78">
         <v>12</v>
       </c>
       <c r="L78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12">
+        <v>0.69154388399724243</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>10</v>
       </c>
@@ -2576,68 +3765,113 @@
         <v>1</v>
       </c>
       <c r="C79">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D79" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E79" t="s">
-        <v>94</v>
+        <v>92</v>
+      </c>
+      <c r="F79">
+        <v>0.98014776902826262</v>
+      </c>
+      <c r="G79">
+        <v>2.357418706147048</v>
+      </c>
+      <c r="H79">
+        <v>0.75</v>
+      </c>
+      <c r="I79">
+        <v>0.24726506167329729</v>
+      </c>
+      <c r="J79">
+        <v>-6.2754085162564019E-2</v>
       </c>
       <c r="K79">
         <v>12</v>
       </c>
       <c r="L79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12">
+        <v>0.70641346768880586</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B80">
         <v>1</v>
       </c>
       <c r="C80">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D80" t="s">
         <v>15</v>
       </c>
       <c r="E80" t="s">
-        <v>95</v>
+        <v>88</v>
+      </c>
+      <c r="F80">
+        <v>0.9796022336557445</v>
+      </c>
+      <c r="G80">
+        <v>2.201157832680178</v>
+      </c>
+      <c r="H80">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I80">
+        <v>0.46117042833360561</v>
+      </c>
+      <c r="J80">
+        <v>-9.0938564542778891E-2</v>
       </c>
       <c r="K80">
         <v>12</v>
       </c>
       <c r="L80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12">
+        <v>0.73555698485190113</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C81">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D81" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E81" t="s">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="F81">
+        <v>0.97749514771290491</v>
+      </c>
+      <c r="G81">
+        <v>2.4644183594344731</v>
+      </c>
+      <c r="H81">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I81">
+        <v>0.19036807564878661</v>
+      </c>
+      <c r="J81">
+        <v>-6.0003199295394882E-2</v>
       </c>
       <c r="K81">
         <v>12</v>
       </c>
       <c r="L81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12">
+        <v>0.67759268158016905</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>10</v>
       </c>
@@ -2645,22 +3879,37 @@
         <v>2</v>
       </c>
       <c r="C82">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D82" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E82" t="s">
-        <v>97</v>
+        <v>93</v>
+      </c>
+      <c r="F82">
+        <v>0.95105308540410194</v>
+      </c>
+      <c r="G82">
+        <v>1.9785909664989849</v>
+      </c>
+      <c r="H82">
+        <v>0.75</v>
+      </c>
+      <c r="I82">
+        <v>0.30799618392548678</v>
+      </c>
+      <c r="J82">
+        <v>-8.2720672939563464E-2</v>
       </c>
       <c r="K82">
         <v>12</v>
       </c>
       <c r="L82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12">
+        <v>0.70613999795773785</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>10</v>
       </c>
@@ -2671,19 +3920,34 @@
         <v>10</v>
       </c>
       <c r="D83" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E83" t="s">
         <v>98</v>
       </c>
+      <c r="F83">
+        <v>0.90908476513539016</v>
+      </c>
+      <c r="G83">
+        <v>1.856624508179844</v>
+      </c>
+      <c r="H83">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I83">
+        <v>0.31135855494595621</v>
+      </c>
+      <c r="J83">
+        <v>-8.1165538300091322E-2</v>
+      </c>
       <c r="K83">
         <v>12</v>
       </c>
       <c r="L83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12">
+        <v>0.66865295883514309</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>10</v>
       </c>
@@ -2691,24 +3955,39 @@
         <v>2</v>
       </c>
       <c r="C84">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D84" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E84" t="s">
         <v>99</v>
       </c>
+      <c r="F84">
+        <v>0.89186237164516602</v>
+      </c>
+      <c r="G84">
+        <v>2.0170336267399609</v>
+      </c>
+      <c r="H84">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I84">
+        <v>0.22105448525019061</v>
+      </c>
+      <c r="J84">
+        <v>-7.5356162171968388E-2</v>
+      </c>
       <c r="K84">
         <v>12</v>
       </c>
       <c r="L84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12">
+        <v>0.65618036672603253</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B85">
         <v>2</v>
@@ -2717,111 +3996,186 @@
         <v>10</v>
       </c>
       <c r="D85" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E85" t="s">
-        <v>100</v>
+        <v>96</v>
+      </c>
+      <c r="F85">
+        <v>0.85350762123644996</v>
+      </c>
+      <c r="G85">
+        <v>1.5831932809476339</v>
+      </c>
+      <c r="H85">
+        <v>0.75</v>
+      </c>
+      <c r="I85">
+        <v>0.1292145218905931</v>
+      </c>
+      <c r="J85">
+        <v>-5.8407541777809373E-2</v>
       </c>
       <c r="K85">
         <v>12</v>
       </c>
       <c r="L85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12">
+        <v>0.68253837689321473</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C86">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D86" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E86" t="s">
         <v>101</v>
       </c>
+      <c r="F86">
+        <v>0.8407159375196982</v>
+      </c>
+      <c r="G86">
+        <v>1.717361642624331</v>
+      </c>
+      <c r="H86">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I86">
+        <v>0.15238640701298639</v>
+      </c>
+      <c r="J86">
+        <v>-5.1076704894659819E-2</v>
+      </c>
       <c r="K86">
         <v>12</v>
       </c>
       <c r="L86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12">
+        <v>0.64668758009380611</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C87">
         <v>20</v>
       </c>
       <c r="D87" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E87" t="s">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="F87">
+        <v>0.83981665576407261</v>
+      </c>
+      <c r="G87">
+        <v>1.9968923281474009</v>
+      </c>
+      <c r="H87">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I87">
+        <v>0.2015509386180013</v>
+      </c>
+      <c r="J87">
+        <v>-8.6395448581803078E-2</v>
       </c>
       <c r="K87">
         <v>12</v>
       </c>
       <c r="L87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12">
+        <v>0.636030358785593</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>10</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C88">
         <v>20</v>
       </c>
       <c r="D88" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E88" t="s">
-        <v>103</v>
+        <v>107</v>
+      </c>
+      <c r="F88">
+        <v>0.81974255481253488</v>
+      </c>
+      <c r="G88">
+        <v>1.929082579026884</v>
+      </c>
+      <c r="H88">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I88">
+        <v>0.1244269720406871</v>
+      </c>
+      <c r="J88">
+        <v>-5.5259692503985533E-2</v>
       </c>
       <c r="K88">
         <v>12</v>
       </c>
       <c r="L88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12">
+        <v>0.60531816981210007</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>10</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D89" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E89" t="s">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="F89">
+        <v>0.8112632092043871</v>
+      </c>
+      <c r="G89">
+        <v>1.369848855009038</v>
+      </c>
+      <c r="H89">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I89">
+        <v>0.13043276144973559</v>
+      </c>
+      <c r="J89">
+        <v>-6.070835226805954E-2</v>
       </c>
       <c r="K89">
         <v>12</v>
       </c>
       <c r="L89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12">
+        <v>0.62609563536848978</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>10</v>
       </c>
@@ -2829,137 +4183,227 @@
         <v>2</v>
       </c>
       <c r="C90">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D90" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E90" t="s">
-        <v>105</v>
+        <v>111</v>
+      </c>
+      <c r="F90">
+        <v>0.7995759884246646</v>
+      </c>
+      <c r="G90">
+        <v>2.1664637518460861</v>
+      </c>
+      <c r="H90">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I90">
+        <v>0.18705057912125861</v>
+      </c>
+      <c r="J90">
+        <v>-5.5991070264318557E-2</v>
       </c>
       <c r="K90">
         <v>12</v>
       </c>
       <c r="L90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12">
+        <v>0.58957330844603684</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C91">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D91" t="s">
         <v>16</v>
       </c>
       <c r="E91" t="s">
-        <v>106</v>
+        <v>104</v>
+      </c>
+      <c r="F91">
+        <v>0.78229647488609022</v>
+      </c>
+      <c r="G91">
+        <v>2.2991446881625239</v>
+      </c>
+      <c r="H91">
+        <v>0.75</v>
+      </c>
+      <c r="I91">
+        <v>0.17992398657291481</v>
+      </c>
+      <c r="J91">
+        <v>-5.1286583384562962E-2</v>
       </c>
       <c r="K91">
         <v>12</v>
       </c>
       <c r="L91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12">
+        <v>0.62885124928168934</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>10</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C92">
         <v>30</v>
       </c>
       <c r="D92" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E92" t="s">
-        <v>107</v>
+        <v>110</v>
+      </c>
+      <c r="F92">
+        <v>0.75622087729036647</v>
+      </c>
+      <c r="G92">
+        <v>2.4130355962632049</v>
+      </c>
+      <c r="H92">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I92">
+        <v>0.27888820389865931</v>
+      </c>
+      <c r="J92">
+        <v>-6.5183225332907949E-2</v>
       </c>
       <c r="K92">
         <v>12</v>
       </c>
       <c r="L92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12">
+        <v>0.5903866430782494</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C93">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D93" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E93" t="s">
-        <v>108</v>
+        <v>106</v>
+      </c>
+      <c r="F93">
+        <v>0.74976466465741254</v>
+      </c>
+      <c r="G93">
+        <v>1.7813177903512241</v>
+      </c>
+      <c r="H93">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I93">
+        <v>9.5507546620691497E-2</v>
+      </c>
+      <c r="J93">
+        <v>-5.8403964885749053E-2</v>
       </c>
       <c r="K93">
         <v>12</v>
       </c>
       <c r="L93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12">
+        <v>0.60776840535440368</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>10</v>
       </c>
       <c r="B94">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C94">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D94" t="s">
         <v>14</v>
       </c>
       <c r="E94" t="s">
-        <v>109</v>
+        <v>115</v>
+      </c>
+      <c r="F94">
+        <v>0.74748793315205686</v>
+      </c>
+      <c r="G94">
+        <v>1.864310451930524</v>
+      </c>
+      <c r="H94">
+        <v>0.5</v>
+      </c>
+      <c r="I94">
+        <v>0.12491019181244881</v>
+      </c>
+      <c r="J94">
+        <v>-6.096874534479222E-2</v>
       </c>
       <c r="K94">
         <v>12</v>
       </c>
       <c r="L94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12">
+        <v>0.55373242330220784</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>10</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D95" t="s">
         <v>15</v>
       </c>
       <c r="E95" t="s">
-        <v>110</v>
+        <v>102</v>
+      </c>
+      <c r="F95">
+        <v>0.7419589741164101</v>
+      </c>
+      <c r="G95">
+        <v>1.441022535612855</v>
+      </c>
+      <c r="H95">
+        <v>0.75</v>
+      </c>
+      <c r="I95">
+        <v>0.22190588668224301</v>
+      </c>
+      <c r="J95">
+        <v>-9.9795600595548525E-2</v>
       </c>
       <c r="K95">
         <v>12</v>
       </c>
       <c r="L95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12">
+        <v>0.64468290565991682</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>10</v>
       </c>
@@ -2970,111 +4414,186 @@
         <v>30</v>
       </c>
       <c r="D96" t="s">
+        <v>15</v>
+      </c>
+      <c r="E96" t="s">
+        <v>108</v>
+      </c>
+      <c r="F96">
+        <v>0.73665998796422871</v>
+      </c>
+      <c r="G96">
+        <v>1.733642771521694</v>
+      </c>
+      <c r="H96">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I96">
+        <v>0.24594558182844789</v>
+      </c>
+      <c r="J96">
+        <v>-6.291348270123015E-2</v>
+      </c>
+      <c r="K96">
+        <v>12</v>
+      </c>
+      <c r="L96">
+        <v>0.6044076687648855</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>5</v>
+      </c>
+      <c r="B97">
+        <v>3</v>
+      </c>
+      <c r="C97">
+        <v>30</v>
+      </c>
+      <c r="D97" t="s">
         <v>16</v>
       </c>
-      <c r="E96" t="s">
-        <v>111</v>
-      </c>
-      <c r="K96">
-        <v>12</v>
-      </c>
-      <c r="L96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12">
-      <c r="A97">
-        <v>10</v>
-      </c>
-      <c r="B97">
-        <v>2</v>
-      </c>
-      <c r="C97">
-        <v>60</v>
-      </c>
-      <c r="D97" t="s">
-        <v>12</v>
-      </c>
       <c r="E97" t="s">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="F97">
+        <v>0.72017701475443685</v>
+      </c>
+      <c r="G97">
+        <v>1.965179221899829</v>
+      </c>
+      <c r="H97">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I97">
+        <v>0.12128671700889471</v>
+      </c>
+      <c r="J97">
+        <v>-5.0892069117589429E-2</v>
       </c>
       <c r="K97">
         <v>12</v>
       </c>
       <c r="L97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12">
+        <v>0.5642451287839465</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B98">
         <v>2</v>
       </c>
       <c r="C98">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D98" t="s">
         <v>13</v>
       </c>
       <c r="E98" t="s">
-        <v>113</v>
+        <v>118</v>
+      </c>
+      <c r="F98">
+        <v>0.64905046710285774</v>
+      </c>
+      <c r="G98">
+        <v>2.0855071877031448</v>
+      </c>
+      <c r="H98">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I98">
+        <v>0.1183223946241477</v>
+      </c>
+      <c r="J98">
+        <v>-6.4613372706529559E-2</v>
       </c>
       <c r="K98">
         <v>12</v>
       </c>
       <c r="L98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12">
+        <v>0.53184893458012361</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>10</v>
       </c>
       <c r="B99">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C99">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D99" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E99" t="s">
+        <v>117</v>
+      </c>
+      <c r="F99">
+        <v>0.63959868767094807</v>
+      </c>
+      <c r="G99">
+        <v>1.9335313974365049</v>
+      </c>
+      <c r="H99">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I99">
+        <v>0.1139675255494446</v>
+      </c>
+      <c r="J99">
+        <v>-7.3619597779637461E-2</v>
+      </c>
+      <c r="K99">
+        <v>12</v>
+      </c>
+      <c r="L99">
+        <v>0.53310529716326394</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>10</v>
+      </c>
+      <c r="B100">
+        <v>1</v>
+      </c>
+      <c r="C100">
+        <v>30</v>
+      </c>
+      <c r="D100" t="s">
+        <v>16</v>
+      </c>
+      <c r="E100" t="s">
         <v>114</v>
       </c>
-      <c r="K99">
-        <v>12</v>
-      </c>
-      <c r="L99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12">
-      <c r="A100">
-        <v>10</v>
-      </c>
-      <c r="B100">
-        <v>2</v>
-      </c>
-      <c r="C100">
-        <v>60</v>
-      </c>
-      <c r="D100" t="s">
-        <v>15</v>
-      </c>
-      <c r="E100" t="s">
-        <v>115</v>
+      <c r="F100">
+        <v>0.63319905376047492</v>
+      </c>
+      <c r="G100">
+        <v>1.9571131693390551</v>
+      </c>
+      <c r="H100">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I100">
+        <v>0.14582686623957419</v>
+      </c>
+      <c r="J100">
+        <v>-5.1456474583388673E-2</v>
       </c>
       <c r="K100">
         <v>12</v>
       </c>
       <c r="L100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12">
+        <v>0.5547299153619164</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>10</v>
       </c>
@@ -3082,73 +4601,118 @@
         <v>2</v>
       </c>
       <c r="C101">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D101" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" t="s">
+        <v>112</v>
+      </c>
+      <c r="F101">
+        <v>0.61403522064779514</v>
+      </c>
+      <c r="G101">
+        <v>1.774827315252979</v>
+      </c>
+      <c r="H101">
+        <v>0.75</v>
+      </c>
+      <c r="I101">
+        <v>0.13315527588911691</v>
+      </c>
+      <c r="J101">
+        <v>-5.8162566004603553E-2</v>
+      </c>
+      <c r="K101">
+        <v>12</v>
+      </c>
+      <c r="L101">
+        <v>0.57872892421699063</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>5</v>
+      </c>
+      <c r="B102">
+        <v>1</v>
+      </c>
+      <c r="C102">
+        <v>30</v>
+      </c>
+      <c r="D102" t="s">
+        <v>15</v>
+      </c>
+      <c r="E102" t="s">
+        <v>119</v>
+      </c>
+      <c r="F102">
+        <v>0.61088336960679501</v>
+      </c>
+      <c r="G102">
+        <v>2.4758034355187761</v>
+      </c>
+      <c r="H102">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I102">
+        <v>0.25594566452802647</v>
+      </c>
+      <c r="J102">
+        <v>-6.7222831705972125E-2</v>
+      </c>
+      <c r="K102">
+        <v>12</v>
+      </c>
+      <c r="L102">
+        <v>0.53066432761054361</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>5</v>
+      </c>
+      <c r="B103">
+        <v>2</v>
+      </c>
+      <c r="C103">
+        <v>30</v>
+      </c>
+      <c r="D103" t="s">
         <v>16</v>
       </c>
-      <c r="E101" t="s">
-        <v>116</v>
-      </c>
-      <c r="K101">
-        <v>12</v>
-      </c>
-      <c r="L101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12">
-      <c r="A102">
-        <v>10</v>
-      </c>
-      <c r="B102">
-        <v>3</v>
-      </c>
-      <c r="C102">
-        <v>10</v>
-      </c>
-      <c r="D102" t="s">
-        <v>12</v>
-      </c>
-      <c r="E102" t="s">
-        <v>117</v>
-      </c>
-      <c r="K102">
-        <v>12</v>
-      </c>
-      <c r="L102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12">
-      <c r="A103">
-        <v>10</v>
-      </c>
-      <c r="B103">
-        <v>3</v>
-      </c>
-      <c r="C103">
-        <v>10</v>
-      </c>
-      <c r="D103" t="s">
-        <v>13</v>
-      </c>
       <c r="E103" t="s">
-        <v>118</v>
+        <v>121</v>
+      </c>
+      <c r="F103">
+        <v>0.58347430729765215</v>
+      </c>
+      <c r="G103">
+        <v>1.6986330620929451</v>
+      </c>
+      <c r="H103">
+        <v>0.5</v>
+      </c>
+      <c r="I103">
+        <v>0.1147929704026856</v>
+      </c>
+      <c r="J103">
+        <v>-5.0433298221211953E-2</v>
       </c>
       <c r="K103">
         <v>12</v>
       </c>
       <c r="L103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12">
+        <v>0.49455711511254902</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>10</v>
       </c>
       <c r="B104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C104">
         <v>10</v>
@@ -3157,62 +4721,107 @@
         <v>14</v>
       </c>
       <c r="E104" t="s">
-        <v>119</v>
+        <v>109</v>
+      </c>
+      <c r="F104">
+        <v>0.57325941784683543</v>
+      </c>
+      <c r="G104">
+        <v>1.6337115355242851</v>
+      </c>
+      <c r="H104">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="I104">
+        <v>0.1562269192825031</v>
+      </c>
+      <c r="J104">
+        <v>-6.9686275567252473E-2</v>
       </c>
       <c r="K104">
         <v>12</v>
       </c>
       <c r="L104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12">
+        <v>0.5932114582254423</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>10</v>
       </c>
       <c r="B105">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C105">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D105" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E105" t="s">
-        <v>120</v>
+        <v>116</v>
+      </c>
+      <c r="F105">
+        <v>0.56573268620743478</v>
+      </c>
+      <c r="G105">
+        <v>2.6509347942102068</v>
+      </c>
+      <c r="H105">
+        <v>0.75</v>
+      </c>
+      <c r="I105">
+        <v>0.17891619654529581</v>
+      </c>
+      <c r="J105">
+        <v>-5.3903158760484952E-2</v>
       </c>
       <c r="K105">
         <v>12</v>
       </c>
       <c r="L105">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12">
+        <v>0.53346381072174531</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>10</v>
       </c>
       <c r="B106">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C106">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D106" t="s">
         <v>16</v>
       </c>
       <c r="E106" t="s">
-        <v>121</v>
+        <v>120</v>
+      </c>
+      <c r="F106">
+        <v>0.55285705665384566</v>
+      </c>
+      <c r="G106">
+        <v>1.8142474536950099</v>
+      </c>
+      <c r="H106">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I106">
+        <v>8.3834906996300737E-2</v>
+      </c>
+      <c r="J106">
+        <v>-6.1887095162115817E-2</v>
       </c>
       <c r="K106">
         <v>12</v>
       </c>
       <c r="L106">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12">
+        <v>0.50274325668027053</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>10</v>
       </c>
@@ -3223,295 +4832,490 @@
         <v>20</v>
       </c>
       <c r="D107" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E107" t="s">
-        <v>122</v>
+        <v>124</v>
+      </c>
+      <c r="F107">
+        <v>0.47561160008821762</v>
+      </c>
+      <c r="G107">
+        <v>2.2437992451558388</v>
+      </c>
+      <c r="H107">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I107">
+        <v>9.1275703587286358E-2</v>
+      </c>
+      <c r="J107">
+        <v>-6.1404438478577128E-2</v>
       </c>
       <c r="K107">
         <v>12</v>
       </c>
       <c r="L107">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12">
+        <v>0.45772878511547599</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B108">
         <v>3</v>
       </c>
       <c r="C108">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D108" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E108" t="s">
-        <v>123</v>
+        <v>125</v>
+      </c>
+      <c r="F108">
+        <v>0.45876817414544901</v>
+      </c>
+      <c r="G108">
+        <v>2.220579371572744</v>
+      </c>
+      <c r="H108">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I108">
+        <v>0.18501287541666969</v>
+      </c>
+      <c r="J108">
+        <v>-9.9708340374607171E-2</v>
       </c>
       <c r="K108">
         <v>12</v>
       </c>
       <c r="L108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12">
+        <v>0.45165821096024028</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B109">
         <v>3</v>
       </c>
       <c r="C109">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D109" t="s">
+        <v>16</v>
+      </c>
+      <c r="E109" t="s">
+        <v>126</v>
+      </c>
+      <c r="F109">
+        <v>0.45856714465636839</v>
+      </c>
+      <c r="G109">
+        <v>1.5896275968857609</v>
+      </c>
+      <c r="H109">
+        <v>0.5</v>
+      </c>
+      <c r="I109">
+        <v>5.1221662590232857E-2</v>
+      </c>
+      <c r="J109">
+        <v>-5.6161315921612033E-2</v>
+      </c>
+      <c r="K109">
+        <v>12</v>
+      </c>
+      <c r="L109">
+        <v>0.44927363071929882</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>10</v>
+      </c>
+      <c r="B110">
+        <v>2</v>
+      </c>
+      <c r="C110">
+        <v>30</v>
+      </c>
+      <c r="D110" t="s">
         <v>14</v>
       </c>
-      <c r="E109" t="s">
-        <v>124</v>
-      </c>
-      <c r="K109">
-        <v>12</v>
-      </c>
-      <c r="L109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12">
-      <c r="A110">
-        <v>10</v>
-      </c>
-      <c r="B110">
-        <v>3</v>
-      </c>
-      <c r="C110">
-        <v>20</v>
-      </c>
-      <c r="D110" t="s">
-        <v>15</v>
-      </c>
       <c r="E110" t="s">
-        <v>125</v>
+        <v>131</v>
+      </c>
+      <c r="F110">
+        <v>0.45849422682827129</v>
+      </c>
+      <c r="G110">
+        <v>1.903856213541149</v>
+      </c>
+      <c r="H110">
+        <v>0.5</v>
+      </c>
+      <c r="I110">
+        <v>0.13988854832488859</v>
+      </c>
+      <c r="J110">
+        <v>-5.8130687360316617E-2</v>
       </c>
       <c r="K110">
         <v>12</v>
       </c>
       <c r="L110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12">
+        <v>0.43670859111303251</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>10</v>
       </c>
       <c r="B111">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C111">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D111" t="s">
         <v>16</v>
       </c>
       <c r="E111" t="s">
-        <v>126</v>
+        <v>123</v>
+      </c>
+      <c r="F111">
+        <v>0.43851824134599199</v>
+      </c>
+      <c r="G111">
+        <v>1.787758981741042</v>
+      </c>
+      <c r="H111">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I111">
+        <v>6.4960037020452582E-2</v>
+      </c>
+      <c r="J111">
+        <v>-6.5387158829714492E-2</v>
       </c>
       <c r="K111">
         <v>12</v>
       </c>
       <c r="L111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12">
+        <v>0.45802061675901379</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B112">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C112">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D112" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E112" t="s">
-        <v>127</v>
+        <v>122</v>
+      </c>
+      <c r="F112">
+        <v>0.43100500384852802</v>
+      </c>
+      <c r="G112">
+        <v>1.8122875143582</v>
+      </c>
+      <c r="H112">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I112">
+        <v>0.21242611383178481</v>
+      </c>
+      <c r="J112">
+        <v>-0.1124923090595626</v>
       </c>
       <c r="K112">
         <v>12</v>
       </c>
       <c r="L112">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12">
+        <v>0.47907672752967462</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>10</v>
       </c>
       <c r="B113">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C113">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D113" t="s">
         <v>13</v>
       </c>
       <c r="E113" t="s">
+        <v>127</v>
+      </c>
+      <c r="F113">
+        <v>0.41244845050261192</v>
+      </c>
+      <c r="G113">
+        <v>2.5655241195912382</v>
+      </c>
+      <c r="H113">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I113">
+        <v>0.13422371060408081</v>
+      </c>
+      <c r="J113">
+        <v>-5.4243232846358243E-2</v>
+      </c>
+      <c r="K113">
+        <v>12</v>
+      </c>
+      <c r="L113">
+        <v>0.44911848287927669</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>10</v>
+      </c>
+      <c r="B114">
+        <v>2</v>
+      </c>
+      <c r="C114">
+        <v>60</v>
+      </c>
+      <c r="D114" t="s">
+        <v>12</v>
+      </c>
+      <c r="E114" t="s">
         <v>128</v>
       </c>
-      <c r="K113">
-        <v>12</v>
-      </c>
-      <c r="L113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12">
-      <c r="A114">
-        <v>10</v>
-      </c>
-      <c r="B114">
-        <v>3</v>
-      </c>
-      <c r="C114">
-        <v>30</v>
-      </c>
-      <c r="D114" t="s">
-        <v>14</v>
-      </c>
-      <c r="E114" t="s">
+      <c r="F114">
+        <v>0.41244845050261192</v>
+      </c>
+      <c r="G114">
+        <v>2.5655241195912382</v>
+      </c>
+      <c r="H114">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I114">
+        <v>0.13422371060408081</v>
+      </c>
+      <c r="J114">
+        <v>-5.4243232846358243E-2</v>
+      </c>
+      <c r="K114">
+        <v>12</v>
+      </c>
+      <c r="L114">
+        <v>0.44911848287927669</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>10</v>
+      </c>
+      <c r="B115">
+        <v>2</v>
+      </c>
+      <c r="C115">
+        <v>60</v>
+      </c>
+      <c r="D115" t="s">
+        <v>16</v>
+      </c>
+      <c r="E115" t="s">
         <v>129</v>
       </c>
-      <c r="K114">
-        <v>12</v>
-      </c>
-      <c r="L114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12">
-      <c r="A115">
-        <v>10</v>
-      </c>
-      <c r="B115">
-        <v>3</v>
-      </c>
-      <c r="C115">
-        <v>30</v>
-      </c>
-      <c r="D115" t="s">
+      <c r="F115">
+        <v>0.41244845050261192</v>
+      </c>
+      <c r="G115">
+        <v>2.5655241195912382</v>
+      </c>
+      <c r="H115">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I115">
+        <v>0.13422371060408081</v>
+      </c>
+      <c r="J115">
+        <v>-5.4243232846358243E-2</v>
+      </c>
+      <c r="K115">
+        <v>12</v>
+      </c>
+      <c r="L115">
+        <v>0.44911848287927669</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>10</v>
+      </c>
+      <c r="B116">
+        <v>2</v>
+      </c>
+      <c r="C116">
+        <v>60</v>
+      </c>
+      <c r="D116" t="s">
         <v>15</v>
       </c>
-      <c r="E115" t="s">
+      <c r="E116" t="s">
         <v>130</v>
       </c>
-      <c r="K115">
-        <v>12</v>
-      </c>
-      <c r="L115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12">
-      <c r="A116">
-        <v>10</v>
-      </c>
-      <c r="B116">
-        <v>3</v>
-      </c>
-      <c r="C116">
-        <v>30</v>
-      </c>
-      <c r="D116" t="s">
-        <v>16</v>
-      </c>
-      <c r="E116" t="s">
-        <v>131</v>
+      <c r="F116">
+        <v>0.41244845050261192</v>
+      </c>
+      <c r="G116">
+        <v>2.5655241195912382</v>
+      </c>
+      <c r="H116">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I116">
+        <v>0.13422371060408081</v>
+      </c>
+      <c r="J116">
+        <v>-5.4243232846358243E-2</v>
       </c>
       <c r="K116">
         <v>12</v>
       </c>
       <c r="L116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12">
+        <v>0.44911848287927669</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B117">
         <v>3</v>
       </c>
       <c r="C117">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D117" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E117" t="s">
-        <v>132</v>
+        <v>133</v>
+      </c>
+      <c r="F117">
+        <v>0.33543133723804569</v>
+      </c>
+      <c r="G117">
+        <v>2.6896166437956568</v>
+      </c>
+      <c r="H117">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I117">
+        <v>0.22046067972146799</v>
+      </c>
+      <c r="J117">
+        <v>-7.7340656198988778E-2</v>
       </c>
       <c r="K117">
         <v>12</v>
       </c>
       <c r="L117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12">
+        <v>0.39048179516876752</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B118">
         <v>3</v>
       </c>
       <c r="C118">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="D118" t="s">
         <v>13</v>
       </c>
       <c r="E118" t="s">
-        <v>133</v>
+        <v>132</v>
+      </c>
+      <c r="F118">
+        <v>0.31733264137820821</v>
+      </c>
+      <c r="G118">
+        <v>2.046042829279977</v>
+      </c>
+      <c r="H118">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I118">
+        <v>5.0973232307624211E-2</v>
+      </c>
+      <c r="J118">
+        <v>-7.1576507299466255E-2</v>
       </c>
       <c r="K118">
         <v>12</v>
       </c>
       <c r="L118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12">
+        <v>0.40042149444068548</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>10</v>
       </c>
       <c r="B119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C119">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D119" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E119" t="s">
         <v>134</v>
       </c>
+      <c r="F119">
+        <v>0.31234567290732362</v>
+      </c>
+      <c r="G119">
+        <v>2.079809455828495</v>
+      </c>
+      <c r="H119">
+        <v>0.5</v>
+      </c>
+      <c r="I119">
+        <v>7.5707420480434884E-2</v>
+      </c>
+      <c r="J119">
+        <v>-5.6498610072926912E-2</v>
+      </c>
       <c r="K119">
         <v>12</v>
       </c>
       <c r="L119">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12">
+        <v>0.3723468927491238</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>10</v>
       </c>
@@ -3519,7 +5323,7 @@
         <v>3</v>
       </c>
       <c r="C120">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D120" t="s">
         <v>15</v>
@@ -3527,37 +5331,134 @@
       <c r="E120" t="s">
         <v>135</v>
       </c>
+      <c r="F120">
+        <v>0.1356245099767521</v>
+      </c>
+      <c r="G120">
+        <v>1.243215596670286</v>
+      </c>
+      <c r="H120">
+        <v>0.5</v>
+      </c>
+      <c r="I120">
+        <v>4.0888393224942803E-2</v>
+      </c>
+      <c r="J120">
+        <v>-8.3253957163236497E-2</v>
+      </c>
       <c r="K120">
         <v>12</v>
       </c>
       <c r="L120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12">
+        <v>0.33798639196971841</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B121">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C121">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D121" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E121" t="s">
         <v>136</v>
       </c>
+      <c r="F121">
+        <v>8.570109035427069E-2</v>
+      </c>
+      <c r="G121">
+        <v>2.08418861625595</v>
+      </c>
+      <c r="H121">
+        <v>0.5</v>
+      </c>
+      <c r="I121">
+        <v>6.5789148818607132E-2</v>
+      </c>
+      <c r="J121">
+        <v>-9.5947214297207026E-2</v>
+      </c>
       <c r="K121">
         <v>12</v>
       </c>
       <c r="L121">
-        <v>0</v>
+        <v>0.2815507517179926</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L121">
+      <sortCondition descending="1" ref="F1"/>
+    </sortState>
+  </autoFilter>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="G1:G1048576">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F1048576">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:H1048576">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I1048576">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1:J1048576">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>